--- a/research/traditional_assets/database/data/poland/poland_green_renewable_energy.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_green_renewable_energy.xlsx
@@ -1528,7 +1528,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1665,22 +1665,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07736046488538606</v>
+        <v>0.07724993000210383</v>
       </c>
       <c r="C2">
-        <v>1682.419888770441</v>
+        <v>1669.935332936083</v>
       </c>
       <c r="D2">
-        <v>1423.419888770441</v>
+        <v>1428.075332936083</v>
       </c>
       <c r="E2">
-        <v>-413.6</v>
+        <v>-396.46</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>17.14</v>
       </c>
       <c r="G2">
         <v>259</v>
@@ -1701,28 +1701,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.862142</v>
       </c>
       <c r="N2">
-        <v>136.9285714285714</v>
+        <v>136.0664294285714</v>
       </c>
       <c r="O2">
-        <v>26.01642857142857</v>
+        <v>25.85262159142857</v>
       </c>
       <c r="P2">
-        <v>110.9121428571429</v>
+        <v>110.2138078371429</v>
       </c>
       <c r="Q2">
-        <v>150.4121428571429</v>
+        <v>149.7138078371429</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07736046488538606</v>
+        <v>0.07761868687081194</v>
       </c>
       <c r="T2">
-        <v>0.5780409979533054</v>
+        <v>0.5827704243001962</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>158.8236873143536</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1747,22 +1747,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07724993000210383</v>
+        <v>0.07713939511882159</v>
       </c>
       <c r="C3">
-        <v>1669.935332936083</v>
+        <v>1657.481329263448</v>
       </c>
       <c r="D3">
-        <v>1428.075332936083</v>
+        <v>1432.761329263448</v>
       </c>
       <c r="E3">
-        <v>-396.46</v>
+        <v>-379.3200000000001</v>
       </c>
       <c r="F3">
-        <v>17.14</v>
+        <v>34.28</v>
       </c>
       <c r="G3">
         <v>259</v>
@@ -1783,28 +1783,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M3">
-        <v>0.862142</v>
+        <v>1.724284</v>
       </c>
       <c r="N3">
-        <v>136.0664294285714</v>
+        <v>135.2042874285714</v>
       </c>
       <c r="O3">
-        <v>25.85262159142857</v>
+        <v>25.68881461142857</v>
       </c>
       <c r="P3">
-        <v>110.2138078371429</v>
+        <v>109.5154728171429</v>
       </c>
       <c r="Q3">
-        <v>149.7138078371429</v>
+        <v>149.0154728171429</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07761868687081194</v>
+        <v>0.07788217869267509</v>
       </c>
       <c r="T3">
-        <v>0.5827704243001962</v>
+        <v>0.5875963695521255</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>158.8236873143536</v>
+        <v>79.4118436571768</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1829,22 +1829,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07713939511882159</v>
+        <v>0.07702886023553936</v>
       </c>
       <c r="C4">
-        <v>1657.481329263448</v>
+        <v>1645.058179498476</v>
       </c>
       <c r="D4">
-        <v>1432.761329263448</v>
+        <v>1437.478179498476</v>
       </c>
       <c r="E4">
-        <v>-379.3200000000001</v>
+        <v>-362.18</v>
       </c>
       <c r="F4">
-        <v>34.28</v>
+        <v>51.41999999999999</v>
       </c>
       <c r="G4">
         <v>259</v>
@@ -1865,28 +1865,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M4">
-        <v>1.724284</v>
+        <v>2.586425999999999</v>
       </c>
       <c r="N4">
-        <v>135.2042874285714</v>
+        <v>134.3421454285715</v>
       </c>
       <c r="O4">
-        <v>25.68881461142857</v>
+        <v>25.52500763142858</v>
       </c>
       <c r="P4">
-        <v>109.5154728171429</v>
+        <v>108.8171377971429</v>
       </c>
       <c r="Q4">
-        <v>149.0154728171429</v>
+        <v>148.3171377971429</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07788217869267509</v>
+        <v>0.07815110333560758</v>
       </c>
       <c r="T4">
-        <v>0.5875963695521255</v>
+        <v>0.5925218188298677</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>79.4118436571768</v>
+        <v>52.94122910478455</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1911,22 +1911,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07702886023553936</v>
+        <v>0.07691832535225711</v>
       </c>
       <c r="C5">
-        <v>1645.058179498476</v>
+        <v>1632.666189373792</v>
       </c>
       <c r="D5">
-        <v>1437.478179498476</v>
+        <v>1442.226189373792</v>
       </c>
       <c r="E5">
-        <v>-362.18</v>
+        <v>-345.04</v>
       </c>
       <c r="F5">
-        <v>51.41999999999999</v>
+        <v>68.56</v>
       </c>
       <c r="G5">
         <v>259</v>
@@ -1947,28 +1947,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M5">
-        <v>2.586425999999999</v>
+        <v>3.448568</v>
       </c>
       <c r="N5">
-        <v>134.3421454285715</v>
+        <v>133.4800034285715</v>
       </c>
       <c r="O5">
-        <v>25.52500763142858</v>
+        <v>25.36120065142858</v>
       </c>
       <c r="P5">
-        <v>108.8171377971429</v>
+        <v>108.1188027771429</v>
       </c>
       <c r="Q5">
-        <v>148.3171377971429</v>
+        <v>147.6188027771429</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07815110333560758</v>
+        <v>0.07842563057526783</v>
       </c>
       <c r="T5">
-        <v>0.5925218188298677</v>
+        <v>0.5975498816342295</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>52.94122910478455</v>
+        <v>39.7059218285884</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1993,22 +1993,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07691832535225711</v>
+        <v>0.07680779046897487</v>
       </c>
       <c r="C6">
-        <v>1632.666189373792</v>
+        <v>1620.305668674758</v>
       </c>
       <c r="D6">
-        <v>1442.226189373792</v>
+        <v>1447.005668674758</v>
       </c>
       <c r="E6">
-        <v>-345.04</v>
+        <v>-327.9</v>
       </c>
       <c r="F6">
-        <v>68.56</v>
+        <v>85.7</v>
       </c>
       <c r="G6">
         <v>259</v>
@@ -2029,28 +2029,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M6">
-        <v>3.448568</v>
+        <v>4.31071</v>
       </c>
       <c r="N6">
-        <v>133.4800034285715</v>
+        <v>132.6178614285714</v>
       </c>
       <c r="O6">
-        <v>25.36120065142858</v>
+        <v>25.19739367142857</v>
       </c>
       <c r="P6">
-        <v>108.1188027771429</v>
+        <v>107.4204677571429</v>
       </c>
       <c r="Q6">
-        <v>147.6188027771429</v>
+        <v>146.9204677571429</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07842563057526783</v>
+        <v>0.07870593733576303</v>
       </c>
       <c r="T6">
-        <v>0.5975498816342295</v>
+        <v>0.6026837983923674</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>39.7059218285884</v>
+        <v>31.76473746287072</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2075,22 +2075,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07680779046897487</v>
+        <v>0.07669725558569265</v>
       </c>
       <c r="C7">
-        <v>1620.305668674758</v>
+        <v>1607.97693130686</v>
       </c>
       <c r="D7">
-        <v>1447.005668674758</v>
+        <v>1451.81693130686</v>
       </c>
       <c r="E7">
-        <v>-327.9</v>
+        <v>-310.76</v>
       </c>
       <c r="F7">
-        <v>85.7</v>
+        <v>102.84</v>
       </c>
       <c r="G7">
         <v>259</v>
@@ -2111,28 +2111,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M7">
-        <v>4.31071</v>
+        <v>5.172852</v>
       </c>
       <c r="N7">
-        <v>132.6178614285714</v>
+        <v>131.7557194285714</v>
       </c>
       <c r="O7">
-        <v>25.19739367142857</v>
+        <v>25.03358669142857</v>
       </c>
       <c r="P7">
-        <v>107.4204677571429</v>
+        <v>106.7221327371429</v>
       </c>
       <c r="Q7">
-        <v>146.9204677571429</v>
+        <v>146.2221327371429</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07870593733576303</v>
+        <v>0.0789922080698858</v>
       </c>
       <c r="T7">
-        <v>0.6026837983923674</v>
+        <v>0.607926947421955</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>31.76473746287072</v>
+        <v>26.47061455239227</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2157,22 +2157,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07669725558569265</v>
+        <v>0.07658672070241043</v>
       </c>
       <c r="C8">
-        <v>1607.97693130686</v>
+        <v>1595.680295364426</v>
       </c>
       <c r="D8">
-        <v>1451.81693130686</v>
+        <v>1456.660295364426</v>
       </c>
       <c r="E8">
-        <v>-310.76</v>
+        <v>-293.62</v>
       </c>
       <c r="F8">
-        <v>102.84</v>
+        <v>119.98</v>
       </c>
       <c r="G8">
         <v>259</v>
@@ -2193,28 +2193,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M8">
-        <v>5.172851999999999</v>
+        <v>6.034993999999999</v>
       </c>
       <c r="N8">
-        <v>131.7557194285714</v>
+        <v>130.8935774285714</v>
       </c>
       <c r="O8">
-        <v>25.03358669142857</v>
+        <v>24.86977971142857</v>
       </c>
       <c r="P8">
-        <v>106.7221327371429</v>
+        <v>106.0237977171429</v>
       </c>
       <c r="Q8">
-        <v>146.2221327371429</v>
+        <v>145.5237977171429</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0789922080698858</v>
+        <v>0.07928463516388218</v>
       </c>
       <c r="T8">
-        <v>0.607926947421955</v>
+        <v>0.6132828523446522</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>26.47061455239227</v>
+        <v>22.6890981877648</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2239,22 +2239,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07658672070241042</v>
+        <v>0.0764761858191282</v>
       </c>
       <c r="C9">
-        <v>1595.680295364426</v>
+        <v>1583.416083200733</v>
       </c>
       <c r="D9">
-        <v>1456.660295364426</v>
+        <v>1461.536083200733</v>
       </c>
       <c r="E9">
-        <v>-293.62</v>
+        <v>-276.48</v>
       </c>
       <c r="F9">
-        <v>119.98</v>
+        <v>137.12</v>
       </c>
       <c r="G9">
         <v>259</v>
@@ -2275,28 +2275,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M9">
-        <v>6.034994</v>
+        <v>6.897136</v>
       </c>
       <c r="N9">
-        <v>130.8935774285714</v>
+        <v>130.0314354285715</v>
       </c>
       <c r="O9">
-        <v>24.86977971142857</v>
+        <v>24.70597273142858</v>
       </c>
       <c r="P9">
-        <v>106.0237977171429</v>
+        <v>105.3254626971429</v>
       </c>
       <c r="Q9">
-        <v>145.5237977171429</v>
+        <v>144.8254626971429</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07928463516388218</v>
+        <v>0.0795834193686176</v>
       </c>
       <c r="T9">
-        <v>0.6132828523446522</v>
+        <v>0.61875518998306</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.6890981877648</v>
+        <v>19.8529609142942</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2321,22 +2321,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0764761858191282</v>
+        <v>0.07636565093584596</v>
       </c>
       <c r="C10">
-        <v>1583.416083200733</v>
+        <v>1571.184621499524</v>
       </c>
       <c r="D10">
-        <v>1461.536083200733</v>
+        <v>1466.444621499524</v>
       </c>
       <c r="E10">
-        <v>-276.48</v>
+        <v>-259.34</v>
       </c>
       <c r="F10">
-        <v>137.12</v>
+        <v>154.26</v>
       </c>
       <c r="G10">
         <v>259</v>
@@ -2357,28 +2357,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M10">
-        <v>6.897136</v>
+        <v>7.759277999999999</v>
       </c>
       <c r="N10">
-        <v>130.0314354285715</v>
+        <v>129.1692934285715</v>
       </c>
       <c r="O10">
-        <v>24.70597273142858</v>
+        <v>24.54216575142858</v>
       </c>
       <c r="P10">
-        <v>105.3254626971429</v>
+        <v>104.6271276771429</v>
       </c>
       <c r="Q10">
-        <v>144.8254626971429</v>
+        <v>144.1271276771429</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0795834193686176</v>
+        <v>0.07988877025917138</v>
       </c>
       <c r="T10">
-        <v>0.61875518998306</v>
+        <v>0.6243477987783559</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.8529609142942</v>
+        <v>17.64707636826151</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2403,22 +2403,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07636565093584596</v>
+        <v>0.07625511605256373</v>
       </c>
       <c r="C11">
-        <v>1571.184621499524</v>
+        <v>1558.986241347975</v>
       </c>
       <c r="D11">
-        <v>1466.444621499524</v>
+        <v>1471.386241347975</v>
       </c>
       <c r="E11">
-        <v>-259.34</v>
+        <v>-242.2</v>
       </c>
       <c r="F11">
-        <v>154.26</v>
+        <v>171.4</v>
       </c>
       <c r="G11">
         <v>259</v>
@@ -2439,28 +2439,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M11">
-        <v>7.759277999999999</v>
+        <v>8.621419999999999</v>
       </c>
       <c r="N11">
-        <v>129.1692934285715</v>
+        <v>128.3071514285714</v>
       </c>
       <c r="O11">
-        <v>24.54216575142858</v>
+        <v>24.37835877142857</v>
       </c>
       <c r="P11">
-        <v>104.6271276771429</v>
+        <v>103.9287926571429</v>
       </c>
       <c r="Q11">
-        <v>144.1271276771429</v>
+        <v>143.4287926571429</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07988877025917138</v>
+        <v>0.0802009067250708</v>
       </c>
       <c r="T11">
-        <v>0.6243477987783559</v>
+        <v>0.630064687769103</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.64707636826151</v>
+        <v>15.88236873143536</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2485,22 +2485,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07625511605256373</v>
+        <v>0.07614458116928149</v>
       </c>
       <c r="C12">
-        <v>1558.986241347975</v>
+        <v>1546.821278311135</v>
       </c>
       <c r="D12">
-        <v>1471.386241347975</v>
+        <v>1476.361278311135</v>
       </c>
       <c r="E12">
-        <v>-242.2</v>
+        <v>-225.06</v>
       </c>
       <c r="F12">
-        <v>171.4</v>
+        <v>188.54</v>
       </c>
       <c r="G12">
         <v>259</v>
@@ -2521,28 +2521,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M12">
-        <v>8.621420000000001</v>
+        <v>9.483561999999999</v>
       </c>
       <c r="N12">
-        <v>128.3071514285714</v>
+        <v>127.4450094285714</v>
       </c>
       <c r="O12">
-        <v>24.37835877142857</v>
+        <v>24.21455179142857</v>
       </c>
       <c r="P12">
-        <v>103.9287926571429</v>
+        <v>103.2304576371429</v>
       </c>
       <c r="Q12">
-        <v>143.4287926571429</v>
+        <v>142.7304576371429</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0802009067250708</v>
+        <v>0.0805200574935747</v>
       </c>
       <c r="T12">
-        <v>0.630064687769103</v>
+        <v>0.6359100461753723</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.88236873143536</v>
+        <v>14.4385170285776</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2567,22 +2567,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07614458116928149</v>
+        <v>0.07603404628599926</v>
       </c>
       <c r="C13">
-        <v>1546.821278311135</v>
+        <v>1534.690072507886</v>
       </c>
       <c r="D13">
-        <v>1476.361278311135</v>
+        <v>1481.370072507887</v>
       </c>
       <c r="E13">
-        <v>-225.06</v>
+        <v>-207.92</v>
       </c>
       <c r="F13">
-        <v>188.54</v>
+        <v>205.68</v>
       </c>
       <c r="G13">
         <v>259</v>
@@ -2603,28 +2603,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M13">
-        <v>9.483561999999999</v>
+        <v>10.345704</v>
       </c>
       <c r="N13">
-        <v>127.4450094285714</v>
+        <v>126.5828674285714</v>
       </c>
       <c r="O13">
-        <v>24.21455179142857</v>
+        <v>24.05074481142858</v>
       </c>
       <c r="P13">
-        <v>103.2304576371429</v>
+        <v>102.5321226171429</v>
       </c>
       <c r="Q13">
-        <v>142.7304576371429</v>
+        <v>142.0321226171429</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0805200574935747</v>
+        <v>0.08084646168863552</v>
       </c>
       <c r="T13">
-        <v>0.6359100461753723</v>
+        <v>0.6418882536363296</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.4385170285776</v>
+        <v>13.23530727619614</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2649,22 +2649,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07603404628599926</v>
+        <v>0.07608146140271702</v>
       </c>
       <c r="C14">
-        <v>1534.690072507886</v>
+        <v>1515.397340353403</v>
       </c>
       <c r="D14">
-        <v>1481.370072507887</v>
+        <v>1479.217340353403</v>
       </c>
       <c r="E14">
-        <v>-207.92</v>
+        <v>-190.78</v>
       </c>
       <c r="F14">
-        <v>205.68</v>
+        <v>222.82</v>
       </c>
       <c r="G14">
         <v>259</v>
@@ -2685,45 +2685,45 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M14">
-        <v>10.345704</v>
+        <v>11.542076</v>
       </c>
       <c r="N14">
-        <v>126.5828674285714</v>
+        <v>125.3864954285714</v>
       </c>
       <c r="O14">
-        <v>24.05074481142858</v>
+        <v>23.82343413142857</v>
       </c>
       <c r="P14">
-        <v>102.5321226171429</v>
+        <v>101.5630612971429</v>
       </c>
       <c r="Q14">
-        <v>142.0321226171429</v>
+        <v>141.0630612971429</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08084646168863552</v>
+        <v>0.08118036942841036</v>
       </c>
       <c r="T14">
-        <v>0.6418882536363296</v>
+        <v>0.6480038911538607</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.19</v>
       </c>
       <c r="W14">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.23530727619614</v>
+        <v>11.8634265992159</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07608146140271702</v>
+        <v>0.07598307651943478</v>
       </c>
       <c r="C15">
-        <v>1515.397340353403</v>
+        <v>1502.731191191183</v>
       </c>
       <c r="D15">
-        <v>1479.217340353403</v>
+        <v>1483.691191191183</v>
       </c>
       <c r="E15">
-        <v>-190.78</v>
+        <v>-173.64</v>
       </c>
       <c r="F15">
-        <v>222.82</v>
+        <v>239.96</v>
       </c>
       <c r="G15">
         <v>259</v>
@@ -2767,28 +2767,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M15">
-        <v>11.542076</v>
+        <v>12.429928</v>
       </c>
       <c r="N15">
-        <v>125.3864954285714</v>
+        <v>124.4986434285714</v>
       </c>
       <c r="O15">
-        <v>23.82343413142857</v>
+        <v>23.65474225142857</v>
       </c>
       <c r="P15">
-        <v>101.5630612971429</v>
+        <v>100.8439011771429</v>
       </c>
       <c r="Q15">
-        <v>141.0630612971429</v>
+        <v>140.3439011771429</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08118036942841036</v>
+        <v>0.08152204246445906</v>
       </c>
       <c r="T15">
-        <v>0.6480038911538607</v>
+        <v>0.6542617527997064</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.8634265992159</v>
+        <v>11.01603898498619</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2813,22 +2813,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07598307651943478</v>
+        <v>0.07588469163615255</v>
       </c>
       <c r="C16">
-        <v>1502.731191191183</v>
+        <v>1490.092186195337</v>
       </c>
       <c r="D16">
-        <v>1483.691191191183</v>
+        <v>1488.192186195337</v>
       </c>
       <c r="E16">
-        <v>-173.64</v>
+        <v>-156.5</v>
       </c>
       <c r="F16">
-        <v>239.96</v>
+        <v>257.1</v>
       </c>
       <c r="G16">
         <v>259</v>
@@ -2849,28 +2849,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M16">
-        <v>12.429928</v>
+        <v>13.31778</v>
       </c>
       <c r="N16">
-        <v>124.4986434285714</v>
+        <v>123.6107914285714</v>
       </c>
       <c r="O16">
-        <v>23.65474225142857</v>
+        <v>23.48605037142858</v>
       </c>
       <c r="P16">
-        <v>100.8439011771429</v>
+        <v>100.1247410571429</v>
       </c>
       <c r="Q16">
-        <v>140.3439011771429</v>
+        <v>139.6247410571429</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08152204246445906</v>
+        <v>0.08187175486606182</v>
       </c>
       <c r="T16">
-        <v>0.6542617527997064</v>
+        <v>0.6606668582489839</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.01603898498619</v>
+        <v>10.28163638598711</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2895,22 +2895,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07588469163615255</v>
+        <v>0.07600662675287032</v>
       </c>
       <c r="C17">
-        <v>1490.092186195337</v>
+        <v>1467.377830784219</v>
       </c>
       <c r="D17">
-        <v>1488.192186195337</v>
+        <v>1482.617830784219</v>
       </c>
       <c r="E17">
-        <v>-156.5000000000001</v>
+        <v>-139.36</v>
       </c>
       <c r="F17">
-        <v>257.1</v>
+        <v>274.24</v>
       </c>
       <c r="G17">
         <v>259</v>
@@ -2931,45 +2931,45 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M17">
-        <v>13.31778</v>
+        <v>14.67184</v>
       </c>
       <c r="N17">
-        <v>123.6107914285714</v>
+        <v>122.2567314285714</v>
       </c>
       <c r="O17">
-        <v>23.48605037142858</v>
+        <v>23.22877897142858</v>
       </c>
       <c r="P17">
-        <v>100.1247410571429</v>
+        <v>99.02795245714287</v>
       </c>
       <c r="Q17">
-        <v>139.6247410571429</v>
+        <v>138.5279524571429</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08187175486606182</v>
+        <v>0.08222979375341705</v>
       </c>
       <c r="T17">
-        <v>0.6606668582489839</v>
+        <v>0.6672244662089584</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.19</v>
       </c>
       <c r="W17">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>10.28163638598711</v>
+        <v>9.332747046626153</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2977,22 +2977,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07600662675287032</v>
+        <v>0.07592201186958808</v>
       </c>
       <c r="C18">
-        <v>1467.377830784219</v>
+        <v>1454.10161745078</v>
       </c>
       <c r="D18">
-        <v>1482.617830784219</v>
+        <v>1486.48161745078</v>
       </c>
       <c r="E18">
-        <v>-139.36</v>
+        <v>-122.22</v>
       </c>
       <c r="F18">
-        <v>274.24</v>
+        <v>291.38</v>
       </c>
       <c r="G18">
         <v>259</v>
@@ -3013,28 +3013,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M18">
-        <v>14.67184</v>
+        <v>15.58883</v>
       </c>
       <c r="N18">
-        <v>122.2567314285714</v>
+        <v>121.3397414285714</v>
       </c>
       <c r="O18">
-        <v>23.22877897142858</v>
+        <v>23.05455087142857</v>
       </c>
       <c r="P18">
-        <v>99.02795245714287</v>
+        <v>98.28519055714287</v>
       </c>
       <c r="Q18">
-        <v>138.5279524571429</v>
+        <v>137.7851905571429</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08222979375341705</v>
+        <v>0.08259646008384107</v>
       </c>
       <c r="T18">
-        <v>0.6672244662089584</v>
+        <v>0.6739400888185707</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.332747046626153</v>
+        <v>8.783761926236378</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3059,22 +3059,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07592201186958808</v>
+        <v>0.07583739698630583</v>
       </c>
       <c r="C19">
-        <v>1454.10161745078</v>
+        <v>1440.845595233592</v>
       </c>
       <c r="D19">
-        <v>1486.48161745078</v>
+        <v>1490.365595233592</v>
       </c>
       <c r="E19">
-        <v>-122.22</v>
+        <v>-105.08</v>
       </c>
       <c r="F19">
-        <v>291.38</v>
+        <v>308.52</v>
       </c>
       <c r="G19">
         <v>259</v>
@@ -3095,28 +3095,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M19">
-        <v>15.58883</v>
+        <v>16.50582</v>
       </c>
       <c r="N19">
-        <v>121.3397414285714</v>
+        <v>120.4227514285714</v>
       </c>
       <c r="O19">
-        <v>23.05455087142857</v>
+        <v>22.88032277142857</v>
       </c>
       <c r="P19">
-        <v>98.28519055714287</v>
+        <v>97.54242865714286</v>
       </c>
       <c r="Q19">
-        <v>137.7851905571429</v>
+        <v>137.0424286571429</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08259646008384107</v>
+        <v>0.08297206949549493</v>
       </c>
       <c r="T19">
-        <v>0.6739400888185707</v>
+        <v>0.6808195071015882</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.783761926236378</v>
+        <v>8.295775152556578</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3141,22 +3141,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07583739698630584</v>
+        <v>0.07575278210302362</v>
       </c>
       <c r="C20">
-        <v>1440.845595233592</v>
+        <v>1427.609922817338</v>
       </c>
       <c r="D20">
-        <v>1490.365595233592</v>
+        <v>1494.269922817338</v>
       </c>
       <c r="E20">
-        <v>-105.08</v>
+        <v>-87.94</v>
       </c>
       <c r="F20">
-        <v>308.52</v>
+        <v>325.66</v>
       </c>
       <c r="G20">
         <v>259</v>
@@ -3177,28 +3177,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M20">
-        <v>16.50582</v>
+        <v>17.42281</v>
       </c>
       <c r="N20">
-        <v>120.4227514285714</v>
+        <v>119.5057614285714</v>
       </c>
       <c r="O20">
-        <v>22.88032277142857</v>
+        <v>22.70609467142857</v>
       </c>
       <c r="P20">
-        <v>97.54242865714286</v>
+        <v>96.79966675714287</v>
       </c>
       <c r="Q20">
-        <v>137.0424286571429</v>
+        <v>136.2996667571429</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08297206949549493</v>
+        <v>0.08335695321360941</v>
       </c>
       <c r="T20">
-        <v>0.6808195071015882</v>
+        <v>0.6878687875644335</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.29577515255658</v>
+        <v>7.85915540768518</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3223,22 +3223,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07575278210302362</v>
+        <v>0.07579776721974139</v>
       </c>
       <c r="C21">
-        <v>1427.609922817338</v>
+        <v>1408.391661599682</v>
       </c>
       <c r="D21">
-        <v>1494.269922817338</v>
+        <v>1492.191661599682</v>
       </c>
       <c r="E21">
-        <v>-87.94</v>
+        <v>-70.80000000000001</v>
       </c>
       <c r="F21">
-        <v>325.66</v>
+        <v>342.8</v>
       </c>
       <c r="G21">
         <v>259</v>
@@ -3259,45 +3259,45 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M21">
-        <v>17.42281</v>
+        <v>18.61404</v>
       </c>
       <c r="N21">
-        <v>119.5057614285714</v>
+        <v>118.3145314285714</v>
       </c>
       <c r="O21">
-        <v>22.70609467142857</v>
+        <v>22.47976097142858</v>
       </c>
       <c r="P21">
-        <v>96.79966675714287</v>
+        <v>95.83477045714287</v>
       </c>
       <c r="Q21">
-        <v>136.2996667571429</v>
+        <v>135.3347704571429</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08335695321360941</v>
+        <v>0.08375145902467673</v>
       </c>
       <c r="T21">
-        <v>0.6878687875644335</v>
+        <v>0.6950943000388499</v>
       </c>
       <c r="U21">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V21">
         <v>0.19</v>
       </c>
       <c r="W21">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>7.85915540768518</v>
+        <v>7.356198408758735</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3305,22 +3305,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07579776721974139</v>
+        <v>0.07571963233645916</v>
       </c>
       <c r="C22">
-        <v>1408.391661599682</v>
+        <v>1394.865112916256</v>
       </c>
       <c r="D22">
-        <v>1492.191661599682</v>
+        <v>1495.805112916256</v>
       </c>
       <c r="E22">
-        <v>-70.80000000000001</v>
+        <v>-53.65999999999997</v>
       </c>
       <c r="F22">
-        <v>342.8</v>
+        <v>359.9400000000001</v>
       </c>
       <c r="G22">
         <v>259</v>
@@ -3341,28 +3341,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M22">
-        <v>18.61404</v>
+        <v>19.544742</v>
       </c>
       <c r="N22">
-        <v>118.3145314285714</v>
+        <v>117.3838294285714</v>
       </c>
       <c r="O22">
-        <v>22.47976097142858</v>
+        <v>22.30292759142857</v>
       </c>
       <c r="P22">
-        <v>95.83477045714287</v>
+        <v>95.08090183714287</v>
       </c>
       <c r="Q22">
-        <v>135.3347704571429</v>
+        <v>134.5809018371429</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08375145902467673</v>
+        <v>0.08415595232463184</v>
       </c>
       <c r="T22">
-        <v>0.6950943000388499</v>
+        <v>0.7025027368797071</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.356198408758735</v>
+        <v>7.00590324643689</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3387,22 +3387,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07571963233645916</v>
+        <v>0.07564149745317693</v>
       </c>
       <c r="C23">
-        <v>1394.865112916256</v>
+        <v>1381.356107188016</v>
       </c>
       <c r="D23">
-        <v>1495.805112916256</v>
+        <v>1499.436107188016</v>
       </c>
       <c r="E23">
-        <v>-53.66000000000003</v>
+        <v>-36.52000000000004</v>
       </c>
       <c r="F23">
-        <v>359.94</v>
+        <v>377.08</v>
       </c>
       <c r="G23">
         <v>259</v>
@@ -3423,28 +3423,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M23">
-        <v>19.544742</v>
+        <v>20.475444</v>
       </c>
       <c r="N23">
-        <v>117.3838294285714</v>
+        <v>116.4531274285714</v>
       </c>
       <c r="O23">
-        <v>22.30292759142857</v>
+        <v>22.12609421142858</v>
       </c>
       <c r="P23">
-        <v>95.08090183714287</v>
+        <v>94.32703321714287</v>
       </c>
       <c r="Q23">
-        <v>134.5809018371429</v>
+        <v>133.8270332171429</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08415595232463184</v>
+        <v>0.08457081724766272</v>
       </c>
       <c r="T23">
-        <v>0.7025027368797071</v>
+        <v>0.7101011336395606</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.00590324643689</v>
+        <v>6.687453098871577</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3469,22 +3469,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07564149745317693</v>
+        <v>0.07556336256989468</v>
       </c>
       <c r="C24">
-        <v>1381.356107188016</v>
+        <v>1367.86477247985</v>
       </c>
       <c r="D24">
-        <v>1499.436107188016</v>
+        <v>1503.08477247985</v>
       </c>
       <c r="E24">
-        <v>-36.52000000000004</v>
+        <v>-19.38</v>
       </c>
       <c r="F24">
-        <v>377.08</v>
+        <v>394.22</v>
       </c>
       <c r="G24">
         <v>259</v>
@@ -3505,28 +3505,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M24">
-        <v>20.475444</v>
+        <v>21.406146</v>
       </c>
       <c r="N24">
-        <v>116.4531274285714</v>
+        <v>115.5224254285714</v>
       </c>
       <c r="O24">
-        <v>22.12609421142858</v>
+        <v>21.94926083142857</v>
       </c>
       <c r="P24">
-        <v>94.32703321714287</v>
+        <v>93.57316459714286</v>
       </c>
       <c r="Q24">
-        <v>133.8270332171429</v>
+        <v>133.0731645971429</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08457081724766272</v>
+        <v>0.0849964578829801</v>
       </c>
       <c r="T24">
-        <v>0.7101011336395606</v>
+        <v>0.7178968913542155</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.687453098871577</v>
+        <v>6.396694268485856</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3551,22 +3551,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07556336256989468</v>
+        <v>0.07548522768661245</v>
       </c>
       <c r="C25">
-        <v>1367.86477247985</v>
+        <v>1354.391238106194</v>
       </c>
       <c r="D25">
-        <v>1503.08477247985</v>
+        <v>1506.751238106194</v>
       </c>
       <c r="E25">
-        <v>-19.38</v>
+        <v>-2.240000000000009</v>
       </c>
       <c r="F25">
-        <v>394.22</v>
+        <v>411.36</v>
       </c>
       <c r="G25">
         <v>259</v>
@@ -3587,28 +3587,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M25">
-        <v>21.406146</v>
+        <v>22.336848</v>
       </c>
       <c r="N25">
-        <v>115.5224254285714</v>
+        <v>114.5917234285714</v>
       </c>
       <c r="O25">
-        <v>21.94926083142857</v>
+        <v>21.77242745142857</v>
       </c>
       <c r="P25">
-        <v>93.57316459714286</v>
+        <v>92.81929597714287</v>
       </c>
       <c r="Q25">
-        <v>133.0731645971429</v>
+        <v>132.3192959771429</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0849964578829801</v>
+        <v>0.08543329958764796</v>
       </c>
       <c r="T25">
-        <v>0.7178968913542155</v>
+        <v>0.7258978005876773</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.396694268485856</v>
+        <v>6.130165340632279</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3633,22 +3633,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07548522768661245</v>
+        <v>0.07560959280333023</v>
       </c>
       <c r="C26">
-        <v>1354.391238106194</v>
+        <v>1331.423816955586</v>
       </c>
       <c r="D26">
-        <v>1506.751238106194</v>
+        <v>1500.923816955586</v>
       </c>
       <c r="E26">
-        <v>-2.240000000000066</v>
+        <v>14.89999999999998</v>
       </c>
       <c r="F26">
-        <v>411.36</v>
+        <v>428.5</v>
       </c>
       <c r="G26">
         <v>259</v>
@@ -3669,45 +3669,45 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M26">
-        <v>22.336848</v>
+        <v>23.69605</v>
       </c>
       <c r="N26">
-        <v>114.5917234285714</v>
+        <v>113.2325214285714</v>
       </c>
       <c r="O26">
-        <v>21.77242745142857</v>
+        <v>21.51417907142858</v>
       </c>
       <c r="P26">
-        <v>92.81929597714287</v>
+        <v>91.71834235714287</v>
       </c>
       <c r="Q26">
-        <v>132.3192959771429</v>
+        <v>131.2183423571429</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08543329958764796</v>
+        <v>0.0858817904044403</v>
       </c>
       <c r="T26">
-        <v>0.7258978005876773</v>
+        <v>0.7341120674006979</v>
       </c>
       <c r="U26">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V26">
         <v>0.19</v>
       </c>
       <c r="W26">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>6.130165340632279</v>
+        <v>5.778539943516807</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3715,22 +3715,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07560959280333023</v>
+        <v>0.07553955792004799</v>
       </c>
       <c r="C27">
-        <v>1331.423816955586</v>
+        <v>1317.559910052909</v>
       </c>
       <c r="D27">
-        <v>1500.923816955586</v>
+        <v>1504.199910052909</v>
       </c>
       <c r="E27">
-        <v>14.89999999999998</v>
+        <v>32.04000000000002</v>
       </c>
       <c r="F27">
-        <v>428.5</v>
+        <v>445.64</v>
       </c>
       <c r="G27">
         <v>259</v>
@@ -3751,28 +3751,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M27">
-        <v>23.69605</v>
+        <v>24.643892</v>
       </c>
       <c r="N27">
-        <v>113.2325214285714</v>
+        <v>112.2846794285714</v>
       </c>
       <c r="O27">
-        <v>21.51417907142858</v>
+        <v>21.33408909142857</v>
       </c>
       <c r="P27">
-        <v>91.71834235714287</v>
+        <v>90.95059033714287</v>
       </c>
       <c r="Q27">
-        <v>131.2183423571429</v>
+        <v>130.4505903371429</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0858817904044403</v>
+        <v>0.08634240259465945</v>
       </c>
       <c r="T27">
-        <v>0.7341120674006979</v>
+        <v>0.7425483414248814</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.778539943516807</v>
+        <v>5.556288407227698</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07553955792004799</v>
+        <v>0.07546952303676575</v>
       </c>
       <c r="C28">
-        <v>1317.559910052909</v>
+        <v>1303.710336008102</v>
       </c>
       <c r="D28">
-        <v>1504.199910052909</v>
+        <v>1507.490336008102</v>
       </c>
       <c r="E28">
-        <v>32.04000000000002</v>
+        <v>49.18000000000001</v>
       </c>
       <c r="F28">
-        <v>445.64</v>
+        <v>462.78</v>
       </c>
       <c r="G28">
         <v>259</v>
@@ -3833,28 +3833,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M28">
-        <v>24.643892</v>
+        <v>25.591734</v>
       </c>
       <c r="N28">
-        <v>112.2846794285714</v>
+        <v>111.3368374285714</v>
       </c>
       <c r="O28">
-        <v>21.33408909142857</v>
+        <v>21.15399911142858</v>
       </c>
       <c r="P28">
-        <v>90.95059033714287</v>
+        <v>90.18283831714287</v>
       </c>
       <c r="Q28">
-        <v>130.4505903371429</v>
+        <v>129.6828383171429</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08634240259465945</v>
+        <v>0.08681563429693939</v>
       </c>
       <c r="T28">
-        <v>0.7425483414248814</v>
+        <v>0.7512157462442477</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.556288407227698</v>
+        <v>5.350499947700747</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3879,22 +3879,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07546952303676575</v>
+        <v>0.07539948815348352</v>
       </c>
       <c r="C29">
-        <v>1303.710336008102</v>
+        <v>1289.875189086424</v>
       </c>
       <c r="D29">
-        <v>1507.490336008102</v>
+        <v>1510.795189086424</v>
       </c>
       <c r="E29">
-        <v>49.18000000000001</v>
+        <v>66.32000000000005</v>
       </c>
       <c r="F29">
-        <v>462.78</v>
+        <v>479.9200000000001</v>
       </c>
       <c r="G29">
         <v>259</v>
@@ -3915,28 +3915,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M29">
-        <v>25.591734</v>
+        <v>26.539576</v>
       </c>
       <c r="N29">
-        <v>111.3368374285714</v>
+        <v>110.3889954285714</v>
       </c>
       <c r="O29">
-        <v>21.15399911142858</v>
+        <v>20.97390913142857</v>
       </c>
       <c r="P29">
-        <v>90.18283831714287</v>
+        <v>89.41508629714286</v>
       </c>
       <c r="Q29">
-        <v>129.6828383171429</v>
+        <v>128.9150862971429</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08681563429693939</v>
+        <v>0.08730201132428267</v>
       </c>
       <c r="T29">
-        <v>0.7512157462442477</v>
+        <v>0.7601239123085967</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.350499947700747</v>
+        <v>5.159410663854291</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3961,22 +3961,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07539948815348352</v>
+        <v>0.0753294532702013</v>
       </c>
       <c r="C30">
-        <v>1289.875189086424</v>
+        <v>1276.054564381579</v>
       </c>
       <c r="D30">
-        <v>1510.795189086424</v>
+        <v>1514.114564381578</v>
       </c>
       <c r="E30">
-        <v>66.32000000000005</v>
+        <v>83.46000000000004</v>
       </c>
       <c r="F30">
-        <v>479.9200000000001</v>
+        <v>497.0600000000001</v>
       </c>
       <c r="G30">
         <v>259</v>
@@ -3997,28 +3997,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M30">
-        <v>26.539576</v>
+        <v>27.48741800000001</v>
       </c>
       <c r="N30">
-        <v>110.3889954285714</v>
+        <v>109.4411534285714</v>
       </c>
       <c r="O30">
-        <v>20.97390913142857</v>
+        <v>20.79381915142858</v>
       </c>
       <c r="P30">
-        <v>89.41508629714286</v>
+        <v>88.64733427714286</v>
       </c>
       <c r="Q30">
-        <v>128.9150862971429</v>
+        <v>128.1473342771429</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08730201132428267</v>
+        <v>0.08780208911295956</v>
       </c>
       <c r="T30">
-        <v>0.7601239123085967</v>
+        <v>0.7692830126282795</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.159410663854291</v>
+        <v>4.981499951307592</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4043,22 +4043,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07532945327020128</v>
+        <v>0.07525941838691905</v>
       </c>
       <c r="C31">
-        <v>1276.054564381579</v>
+        <v>1262.248557824832</v>
       </c>
       <c r="D31">
-        <v>1514.114564381579</v>
+        <v>1517.448557824831</v>
       </c>
       <c r="E31">
-        <v>83.45999999999992</v>
+        <v>100.5999999999999</v>
       </c>
       <c r="F31">
-        <v>497.0599999999999</v>
+        <v>514.1999999999999</v>
       </c>
       <c r="G31">
         <v>259</v>
@@ -4079,28 +4079,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M31">
-        <v>27.487418</v>
+        <v>28.43526</v>
       </c>
       <c r="N31">
-        <v>109.4411534285715</v>
+        <v>108.4933114285714</v>
       </c>
       <c r="O31">
-        <v>20.79381915142858</v>
+        <v>20.61372917142857</v>
       </c>
       <c r="P31">
-        <v>88.64733427714287</v>
+        <v>87.87958225714287</v>
       </c>
       <c r="Q31">
-        <v>128.1473342771429</v>
+        <v>127.3795822571429</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08780208911295956</v>
+        <v>0.08831645483845579</v>
       </c>
       <c r="T31">
-        <v>0.7692830126282793</v>
+        <v>0.7787038015285244</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.981499951307593</v>
+        <v>4.815449952930674</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4125,22 +4125,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07525941838691905</v>
+        <v>0.07518938350363683</v>
       </c>
       <c r="C32">
-        <v>1262.248557824832</v>
+        <v>1248.457266194252</v>
       </c>
       <c r="D32">
-        <v>1517.448557824831</v>
+        <v>1520.797266194252</v>
       </c>
       <c r="E32">
-        <v>100.5999999999999</v>
+        <v>117.74</v>
       </c>
       <c r="F32">
-        <v>514.1999999999999</v>
+        <v>531.34</v>
       </c>
       <c r="G32">
         <v>259</v>
@@ -4161,28 +4161,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M32">
-        <v>28.43526</v>
+        <v>29.383102</v>
       </c>
       <c r="N32">
-        <v>108.4933114285714</v>
+        <v>107.5454694285714</v>
       </c>
       <c r="O32">
-        <v>20.61372917142857</v>
+        <v>20.43363919142857</v>
       </c>
       <c r="P32">
-        <v>87.87958225714287</v>
+        <v>87.11183023714287</v>
       </c>
       <c r="Q32">
-        <v>127.3795822571429</v>
+        <v>126.6118302371429</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08831645483845579</v>
+        <v>0.08884572971541568</v>
       </c>
       <c r="T32">
-        <v>0.7787038015285244</v>
+        <v>0.788397656773704</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.815449952930674</v>
+        <v>4.660112857674844</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4207,22 +4207,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07518938350363683</v>
+        <v>0.07511934862035459</v>
       </c>
       <c r="C33">
-        <v>1248.457266194252</v>
+        <v>1234.680787124084</v>
       </c>
       <c r="D33">
-        <v>1520.797266194252</v>
+        <v>1524.160787124084</v>
       </c>
       <c r="E33">
-        <v>117.74</v>
+        <v>134.88</v>
       </c>
       <c r="F33">
-        <v>531.34</v>
+        <v>548.48</v>
       </c>
       <c r="G33">
         <v>259</v>
@@ -4243,28 +4243,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M33">
-        <v>29.383102</v>
+        <v>30.330944</v>
       </c>
       <c r="N33">
-        <v>107.5454694285714</v>
+        <v>106.5976274285714</v>
       </c>
       <c r="O33">
-        <v>20.43363919142857</v>
+        <v>20.25354921142857</v>
       </c>
       <c r="P33">
-        <v>87.11183023714287</v>
+        <v>86.34407821714287</v>
       </c>
       <c r="Q33">
-        <v>126.6118302371429</v>
+        <v>125.8440782171429</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08884572971541568</v>
+        <v>0.08939057150052146</v>
       </c>
       <c r="T33">
-        <v>0.788397656773704</v>
+        <v>0.7983766254084478</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.660112857674844</v>
+        <v>4.514484330872506</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4289,22 +4289,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07511934862035459</v>
+        <v>0.07571756373707235</v>
       </c>
       <c r="C34">
-        <v>1234.680787124084</v>
+        <v>1189.281015847196</v>
       </c>
       <c r="D34">
-        <v>1524.160787124084</v>
+        <v>1495.901015847196</v>
       </c>
       <c r="E34">
-        <v>134.88</v>
+        <v>152.02</v>
       </c>
       <c r="F34">
-        <v>548.48</v>
+        <v>565.62</v>
       </c>
       <c r="G34">
         <v>259</v>
@@ -4325,45 +4325,45 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M34">
-        <v>30.330944</v>
+        <v>32.692836</v>
       </c>
       <c r="N34">
-        <v>106.5976274285714</v>
+        <v>104.2357354285714</v>
       </c>
       <c r="O34">
-        <v>20.25354921142857</v>
+        <v>19.80478973142857</v>
       </c>
       <c r="P34">
-        <v>86.34407821714287</v>
+        <v>84.43094569714287</v>
       </c>
       <c r="Q34">
-        <v>125.8440782171429</v>
+        <v>123.9309456971429</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08939057150052146</v>
+        <v>0.08995167721951097</v>
       </c>
       <c r="T34">
-        <v>0.7983766254084478</v>
+        <v>0.8086534737039301</v>
       </c>
       <c r="U34">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V34">
         <v>0.19</v>
       </c>
       <c r="W34">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.514484330872506</v>
+        <v>4.188335677839985</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4371,22 +4371,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07571756373707235</v>
+        <v>0.07566777885379011</v>
       </c>
       <c r="C35">
-        <v>1189.281015847196</v>
+        <v>1174.452822333948</v>
       </c>
       <c r="D35">
-        <v>1495.901015847196</v>
+        <v>1498.212822333948</v>
       </c>
       <c r="E35">
-        <v>152.02</v>
+        <v>169.16</v>
       </c>
       <c r="F35">
-        <v>565.62</v>
+        <v>582.76</v>
       </c>
       <c r="G35">
         <v>259</v>
@@ -4407,28 +4407,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M35">
-        <v>32.692836</v>
+        <v>33.683528</v>
       </c>
       <c r="N35">
-        <v>104.2357354285714</v>
+        <v>103.2450434285714</v>
       </c>
       <c r="O35">
-        <v>19.80478973142857</v>
+        <v>19.61655825142858</v>
       </c>
       <c r="P35">
-        <v>84.43094569714287</v>
+        <v>83.62848517714288</v>
       </c>
       <c r="Q35">
-        <v>123.9309456971429</v>
+        <v>123.1284851771429</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08995167721951097</v>
+        <v>0.09052978614210624</v>
       </c>
       <c r="T35">
-        <v>0.8086534737039301</v>
+        <v>0.8192417416447303</v>
       </c>
       <c r="U35">
         <v>0.0578</v>
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.188335677839985</v>
+        <v>4.065149334374103</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4453,22 +4453,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07566777885379011</v>
+        <v>0.07661024397050788</v>
       </c>
       <c r="C36">
-        <v>1174.452822333948</v>
+        <v>1114.72685928505</v>
       </c>
       <c r="D36">
-        <v>1498.212822333948</v>
+        <v>1455.62685928505</v>
       </c>
       <c r="E36">
-        <v>169.16</v>
+        <v>186.3000000000001</v>
       </c>
       <c r="F36">
-        <v>582.76</v>
+        <v>599.9000000000001</v>
       </c>
       <c r="G36">
         <v>259</v>
@@ -4489,45 +4489,45 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M36">
-        <v>33.683528</v>
+        <v>36.77387</v>
       </c>
       <c r="N36">
-        <v>103.2450434285714</v>
+        <v>100.1547014285714</v>
       </c>
       <c r="O36">
-        <v>19.61655825142858</v>
+        <v>19.02939327142857</v>
       </c>
       <c r="P36">
-        <v>83.62848517714288</v>
+        <v>81.12530815714287</v>
       </c>
       <c r="Q36">
-        <v>123.1284851771429</v>
+        <v>120.6253081571429</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09052978614210624</v>
+        <v>0.09112568303155058</v>
       </c>
       <c r="T36">
-        <v>0.8192417416447303</v>
+        <v>0.8301558024452471</v>
       </c>
       <c r="U36">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V36">
         <v>0.19</v>
       </c>
       <c r="W36">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.065149334374103</v>
+        <v>3.723529001124207</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4535,22 +4535,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07661024397050788</v>
+        <v>0.07658880908722564</v>
       </c>
       <c r="C37">
-        <v>1114.72685928505</v>
+        <v>1098.528488038586</v>
       </c>
       <c r="D37">
-        <v>1455.62685928505</v>
+        <v>1456.568488038586</v>
       </c>
       <c r="E37">
-        <v>186.3000000000001</v>
+        <v>203.4400000000001</v>
       </c>
       <c r="F37">
-        <v>599.9000000000001</v>
+        <v>617.0400000000001</v>
       </c>
       <c r="G37">
         <v>259</v>
@@ -4571,28 +4571,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M37">
-        <v>36.77387</v>
+        <v>37.824552</v>
       </c>
       <c r="N37">
-        <v>100.1547014285714</v>
+        <v>99.10401942857143</v>
       </c>
       <c r="O37">
-        <v>19.02939327142857</v>
+        <v>18.82976369142857</v>
       </c>
       <c r="P37">
-        <v>81.12530815714287</v>
+        <v>80.27425573714287</v>
       </c>
       <c r="Q37">
-        <v>120.6253081571429</v>
+        <v>119.7742557371429</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09112568303155058</v>
+        <v>0.09174020169879007</v>
       </c>
       <c r="T37">
-        <v>0.8301558024452471</v>
+        <v>0.8414109276457803</v>
       </c>
       <c r="U37">
         <v>0.0613</v>
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.723529001124207</v>
+        <v>3.620097639981867</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4617,22 +4617,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07658880908722565</v>
+        <v>0.07656737420394343</v>
       </c>
       <c r="C38">
-        <v>1098.528488038586</v>
+        <v>1082.331335838952</v>
       </c>
       <c r="D38">
-        <v>1456.568488038586</v>
+        <v>1457.511335838952</v>
       </c>
       <c r="E38">
-        <v>203.4399999999999</v>
+        <v>220.5799999999999</v>
       </c>
       <c r="F38">
-        <v>617.04</v>
+        <v>634.1799999999999</v>
       </c>
       <c r="G38">
         <v>259</v>
@@ -4653,28 +4653,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M38">
-        <v>37.824552</v>
+        <v>38.875234</v>
       </c>
       <c r="N38">
-        <v>99.10401942857145</v>
+        <v>98.05333742857144</v>
       </c>
       <c r="O38">
-        <v>18.82976369142857</v>
+        <v>18.63013411142857</v>
       </c>
       <c r="P38">
-        <v>80.27425573714288</v>
+        <v>79.42320331714286</v>
       </c>
       <c r="Q38">
-        <v>119.7742557371429</v>
+        <v>118.9232033171429</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09174020169879007</v>
+        <v>0.09237422889514829</v>
       </c>
       <c r="T38">
-        <v>0.8414109276457802</v>
+        <v>0.8530233584082351</v>
       </c>
       <c r="U38">
         <v>0.0613</v>
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.620097639981868</v>
+        <v>3.522257163225601</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4699,22 +4699,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07656737420394343</v>
+        <v>0.07740777932066119</v>
       </c>
       <c r="C39">
-        <v>1082.331335838952</v>
+        <v>1029.116390900403</v>
       </c>
       <c r="D39">
-        <v>1457.511335838952</v>
+        <v>1421.436390900403</v>
       </c>
       <c r="E39">
-        <v>220.5799999999999</v>
+        <v>237.72</v>
       </c>
       <c r="F39">
-        <v>634.1799999999999</v>
+        <v>651.3200000000001</v>
       </c>
       <c r="G39">
         <v>259</v>
@@ -4735,45 +4735,45 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M39">
-        <v>38.875234</v>
+        <v>41.74961200000001</v>
       </c>
       <c r="N39">
-        <v>98.05333742857144</v>
+        <v>95.17895942857143</v>
       </c>
       <c r="O39">
-        <v>18.63013411142857</v>
+        <v>18.08400229142857</v>
       </c>
       <c r="P39">
-        <v>79.42320331714286</v>
+        <v>77.09495713714286</v>
       </c>
       <c r="Q39">
-        <v>118.9232033171429</v>
+        <v>116.5949571371429</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09237422889514829</v>
+        <v>0.09302870858171158</v>
       </c>
       <c r="T39">
-        <v>0.8530233584082351</v>
+        <v>0.8650103837114143</v>
       </c>
       <c r="U39">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V39">
         <v>0.19</v>
       </c>
       <c r="W39">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.522257163225601</v>
+        <v>3.279756741896701</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4781,22 +4781,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07740777932066119</v>
+        <v>0.07740902443737896</v>
       </c>
       <c r="C40">
-        <v>1029.116390900403</v>
+        <v>1011.92426823496</v>
       </c>
       <c r="D40">
-        <v>1421.436390900403</v>
+        <v>1421.38426823496</v>
       </c>
       <c r="E40">
-        <v>237.72</v>
+        <v>254.86</v>
       </c>
       <c r="F40">
-        <v>651.3200000000001</v>
+        <v>668.46</v>
       </c>
       <c r="G40">
         <v>259</v>
@@ -4817,28 +4817,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M40">
-        <v>41.74961200000001</v>
+        <v>42.848286</v>
       </c>
       <c r="N40">
-        <v>95.17895942857143</v>
+        <v>94.08028542857144</v>
       </c>
       <c r="O40">
-        <v>18.08400229142857</v>
+        <v>17.87525423142857</v>
       </c>
       <c r="P40">
-        <v>77.09495713714286</v>
+        <v>76.20503119714287</v>
       </c>
       <c r="Q40">
-        <v>116.5949571371429</v>
+        <v>115.7050311971429</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09302870858171158</v>
+        <v>0.09370464661865402</v>
       </c>
       <c r="T40">
-        <v>0.8650103837114143</v>
+        <v>0.8773904262376484</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.279756741896701</v>
+        <v>3.195660415181401</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07740902443737896</v>
+        <v>0.07741026955409672</v>
       </c>
       <c r="C41">
-        <v>1011.92426823496</v>
+        <v>994.7321493919516</v>
       </c>
       <c r="D41">
-        <v>1421.38426823496</v>
+        <v>1421.332149391952</v>
       </c>
       <c r="E41">
-        <v>254.86</v>
+        <v>272</v>
       </c>
       <c r="F41">
-        <v>668.46</v>
+        <v>685.6</v>
       </c>
       <c r="G41">
         <v>259</v>
@@ -4899,28 +4899,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M41">
-        <v>42.848286</v>
+        <v>43.94696</v>
       </c>
       <c r="N41">
-        <v>94.08028542857144</v>
+        <v>92.98161142857144</v>
       </c>
       <c r="O41">
-        <v>17.87525423142857</v>
+        <v>17.66650617142857</v>
       </c>
       <c r="P41">
-        <v>76.20503119714287</v>
+        <v>75.31510525714287</v>
       </c>
       <c r="Q41">
-        <v>115.7050311971429</v>
+        <v>114.8151052571429</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09370464661865402</v>
+        <v>0.09440311592349453</v>
       </c>
       <c r="T41">
-        <v>0.8773904262376484</v>
+        <v>0.8901831368480904</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.195660415181401</v>
+        <v>3.115768904801866</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4945,22 +4945,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07741026955409672</v>
+        <v>0.07741151467081447</v>
       </c>
       <c r="C42">
-        <v>994.7321493919516</v>
+        <v>977.5400343709555</v>
       </c>
       <c r="D42">
-        <v>1421.332149391952</v>
+        <v>1421.280034370955</v>
       </c>
       <c r="E42">
-        <v>272</v>
+        <v>289.14</v>
       </c>
       <c r="F42">
-        <v>685.6</v>
+        <v>702.74</v>
       </c>
       <c r="G42">
         <v>259</v>
@@ -4981,28 +4981,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M42">
-        <v>43.94696</v>
+        <v>45.04563400000001</v>
       </c>
       <c r="N42">
-        <v>92.98161142857144</v>
+        <v>91.88293742857144</v>
       </c>
       <c r="O42">
-        <v>17.66650617142857</v>
+        <v>17.45775811142857</v>
       </c>
       <c r="P42">
-        <v>75.31510525714287</v>
+        <v>74.42517931714286</v>
       </c>
       <c r="Q42">
-        <v>114.8151052571429</v>
+        <v>113.9251793171429</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09440311592349453</v>
+        <v>0.09512526215392285</v>
       </c>
       <c r="T42">
-        <v>0.8901831368480904</v>
+        <v>0.903409498665666</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.115768904801866</v>
+        <v>3.039774541270114</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5027,22 +5027,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07741151467081447</v>
+        <v>0.08006631978753226</v>
       </c>
       <c r="C43">
-        <v>977.5400343709555</v>
+        <v>857.3427439717477</v>
       </c>
       <c r="D43">
-        <v>1421.280034370955</v>
+        <v>1318.222743971748</v>
       </c>
       <c r="E43">
-        <v>289.14</v>
+        <v>306.2800000000001</v>
       </c>
       <c r="F43">
-        <v>702.74</v>
+        <v>719.8800000000001</v>
       </c>
       <c r="G43">
         <v>259</v>
@@ -5063,45 +5063,45 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M43">
-        <v>45.04563400000001</v>
+        <v>51.75937200000001</v>
       </c>
       <c r="N43">
-        <v>91.88293742857144</v>
+        <v>85.16919942857143</v>
       </c>
       <c r="O43">
-        <v>17.45775811142857</v>
+        <v>16.18214789142857</v>
       </c>
       <c r="P43">
-        <v>74.42517931714286</v>
+        <v>68.98705153714286</v>
       </c>
       <c r="Q43">
-        <v>113.9251793171429</v>
+        <v>108.4870515371429</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09512526215392285</v>
+        <v>0.09587230997850388</v>
       </c>
       <c r="T43">
-        <v>0.903409498665666</v>
+        <v>0.9170919419252271</v>
       </c>
       <c r="U43">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V43">
         <v>0.19</v>
       </c>
       <c r="W43">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>3.039774541270114</v>
+        <v>2.645483631999465</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5109,22 +5109,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08006631978753226</v>
+        <v>0.08013074490425003</v>
       </c>
       <c r="C44">
-        <v>857.3427439717478</v>
+        <v>837.8872326627456</v>
       </c>
       <c r="D44">
-        <v>1318.222743971748</v>
+        <v>1315.907232662746</v>
       </c>
       <c r="E44">
-        <v>306.28</v>
+        <v>323.42</v>
       </c>
       <c r="F44">
-        <v>719.88</v>
+        <v>737.02</v>
       </c>
       <c r="G44">
         <v>259</v>
@@ -5145,28 +5145,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M44">
-        <v>51.75937200000001</v>
+        <v>52.99173800000001</v>
       </c>
       <c r="N44">
-        <v>85.16919942857143</v>
+        <v>83.93683342857145</v>
       </c>
       <c r="O44">
-        <v>16.18214789142857</v>
+        <v>15.94799835142858</v>
       </c>
       <c r="P44">
-        <v>68.98705153714286</v>
+        <v>67.98883507714287</v>
       </c>
       <c r="Q44">
-        <v>108.4870515371429</v>
+        <v>107.4888350771429</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09587230997850388</v>
+        <v>0.09664557000745616</v>
       </c>
       <c r="T44">
-        <v>0.917091941925227</v>
+        <v>0.9312544709131936</v>
       </c>
       <c r="U44">
         <v>0.07190000000000001</v>
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.645483631999465</v>
+        <v>2.583960756836687</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5191,22 +5191,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08013074490425003</v>
+        <v>0.08019517002096779</v>
       </c>
       <c r="C45">
-        <v>837.8872326627456</v>
+        <v>818.4398416677149</v>
       </c>
       <c r="D45">
-        <v>1315.907232662746</v>
+        <v>1313.599841667715</v>
       </c>
       <c r="E45">
-        <v>323.42</v>
+        <v>340.5599999999999</v>
       </c>
       <c r="F45">
-        <v>737.02</v>
+        <v>754.16</v>
       </c>
       <c r="G45">
         <v>259</v>
@@ -5227,28 +5227,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M45">
-        <v>52.99173800000001</v>
+        <v>54.224104</v>
       </c>
       <c r="N45">
-        <v>83.93683342857145</v>
+        <v>82.70446742857143</v>
       </c>
       <c r="O45">
-        <v>15.94799835142858</v>
+        <v>15.71384881142857</v>
       </c>
       <c r="P45">
-        <v>67.98883507714287</v>
+        <v>66.99061861714286</v>
       </c>
       <c r="Q45">
-        <v>107.4888350771429</v>
+        <v>106.4906186171429</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09664557000745616</v>
+        <v>0.0974464464660139</v>
       </c>
       <c r="T45">
-        <v>0.9312544709131936</v>
+        <v>0.9459228045078735</v>
       </c>
       <c r="U45">
         <v>0.07190000000000001</v>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.583960756836687</v>
+        <v>2.52523437599949</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5273,22 +5273,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08019517002096779</v>
+        <v>0.08168114513768555</v>
       </c>
       <c r="C46">
-        <v>818.4398416677149</v>
+        <v>750.237974432266</v>
       </c>
       <c r="D46">
-        <v>1313.599841667715</v>
+        <v>1262.537974432266</v>
       </c>
       <c r="E46">
-        <v>340.5599999999999</v>
+        <v>357.7</v>
       </c>
       <c r="F46">
-        <v>754.16</v>
+        <v>771.3000000000001</v>
       </c>
       <c r="G46">
         <v>259</v>
@@ -5309,45 +5309,45 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M46">
-        <v>54.224104</v>
+        <v>58.46454000000001</v>
       </c>
       <c r="N46">
-        <v>82.70446742857143</v>
+        <v>78.46403142857145</v>
       </c>
       <c r="O46">
-        <v>15.71384881142857</v>
+        <v>14.90816597142858</v>
       </c>
       <c r="P46">
-        <v>66.99061861714286</v>
+        <v>63.55586545714287</v>
       </c>
       <c r="Q46">
-        <v>106.4906186171429</v>
+        <v>103.0558654571429</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.0974464464660139</v>
+        <v>0.09827644570488281</v>
       </c>
       <c r="T46">
-        <v>0.9459228045078735</v>
+        <v>0.9611245320514505</v>
       </c>
       <c r="U46">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V46">
         <v>0.19</v>
       </c>
       <c r="W46">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.52523437599949</v>
+        <v>2.342079000853705</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5355,22 +5355,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08168114513768555</v>
+        <v>0.08177716025440332</v>
       </c>
       <c r="C47">
-        <v>750.237974432266</v>
+        <v>729.9348469399893</v>
       </c>
       <c r="D47">
-        <v>1262.537974432266</v>
+        <v>1259.374846939989</v>
       </c>
       <c r="E47">
-        <v>357.7</v>
+        <v>374.84</v>
       </c>
       <c r="F47">
-        <v>771.3000000000001</v>
+        <v>788.4400000000001</v>
       </c>
       <c r="G47">
         <v>259</v>
@@ -5391,28 +5391,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M47">
-        <v>58.46454000000001</v>
+        <v>59.76375200000001</v>
       </c>
       <c r="N47">
-        <v>78.46403142857145</v>
+        <v>77.16481942857143</v>
       </c>
       <c r="O47">
-        <v>14.90816597142858</v>
+        <v>14.66131569142857</v>
       </c>
       <c r="P47">
-        <v>63.55586545714287</v>
+        <v>62.50350373714286</v>
       </c>
       <c r="Q47">
-        <v>103.0558654571429</v>
+        <v>102.0035037371429</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09827644570488281</v>
+        <v>0.09913718565630245</v>
       </c>
       <c r="T47">
-        <v>0.9611245320514505</v>
+        <v>0.9768892865410862</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.342079000853705</v>
+        <v>2.29116423996558</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5437,22 +5437,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08177716025440332</v>
+        <v>0.08187317537112108</v>
       </c>
       <c r="C48">
-        <v>729.9348469399893</v>
+        <v>709.6475294608621</v>
       </c>
       <c r="D48">
-        <v>1259.374846939989</v>
+        <v>1256.227529460862</v>
       </c>
       <c r="E48">
-        <v>374.84</v>
+        <v>391.98</v>
       </c>
       <c r="F48">
-        <v>788.4400000000001</v>
+        <v>805.58</v>
       </c>
       <c r="G48">
         <v>259</v>
@@ -5473,28 +5473,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M48">
-        <v>59.76375200000001</v>
+        <v>61.06296400000001</v>
       </c>
       <c r="N48">
-        <v>77.16481942857143</v>
+        <v>75.86560742857144</v>
       </c>
       <c r="O48">
-        <v>14.66131569142857</v>
+        <v>14.41446541142857</v>
       </c>
       <c r="P48">
-        <v>62.50350373714286</v>
+        <v>61.45114201714286</v>
       </c>
       <c r="Q48">
-        <v>102.0035037371429</v>
+        <v>100.9511420171429</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09913718565630245</v>
+        <v>0.1000304063606058</v>
       </c>
       <c r="T48">
-        <v>0.9768892865410862</v>
+        <v>0.9932489374265572</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.29116423996558</v>
+        <v>2.242416064647164</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5519,22 +5519,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08187317537112108</v>
+        <v>0.08196919048783886</v>
       </c>
       <c r="C49">
-        <v>709.6475294608621</v>
+        <v>689.3759037574412</v>
       </c>
       <c r="D49">
-        <v>1256.227529460862</v>
+        <v>1253.095903757441</v>
       </c>
       <c r="E49">
-        <v>391.98</v>
+        <v>409.12</v>
       </c>
       <c r="F49">
-        <v>805.58</v>
+        <v>822.72</v>
       </c>
       <c r="G49">
         <v>259</v>
@@ -5555,28 +5555,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M49">
-        <v>61.06296400000001</v>
+        <v>62.36217600000001</v>
       </c>
       <c r="N49">
-        <v>75.86560742857144</v>
+        <v>74.56639542857144</v>
       </c>
       <c r="O49">
-        <v>14.41446541142857</v>
+        <v>14.16761513142857</v>
       </c>
       <c r="P49">
-        <v>61.45114201714286</v>
+        <v>60.39878029714286</v>
       </c>
       <c r="Q49">
-        <v>100.9511420171429</v>
+        <v>99.89878029714286</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1000304063606058</v>
+        <v>0.1009579817073824</v>
       </c>
       <c r="T49">
-        <v>0.9932489374265572</v>
+        <v>1.010237805653777</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.242416064647164</v>
+        <v>2.195699063300348</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5601,22 +5601,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08196919048783885</v>
+        <v>0.08206520560455663</v>
       </c>
       <c r="C50">
-        <v>689.3759037574417</v>
+        <v>669.1198527683601</v>
       </c>
       <c r="D50">
-        <v>1253.095903757442</v>
+        <v>1249.97985276836</v>
       </c>
       <c r="E50">
-        <v>409.1199999999999</v>
+        <v>426.26</v>
       </c>
       <c r="F50">
-        <v>822.7199999999999</v>
+        <v>839.86</v>
       </c>
       <c r="G50">
         <v>259</v>
@@ -5637,28 +5637,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M50">
-        <v>62.362176</v>
+        <v>63.66138800000001</v>
       </c>
       <c r="N50">
-        <v>74.56639542857144</v>
+        <v>73.26718342857143</v>
       </c>
       <c r="O50">
-        <v>14.16761513142857</v>
+        <v>13.92076485142857</v>
       </c>
       <c r="P50">
-        <v>60.39878029714286</v>
+        <v>59.34641857714286</v>
       </c>
       <c r="Q50">
-        <v>99.89878029714286</v>
+        <v>98.84641857714286</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1009579817073824</v>
+        <v>0.1019219325579541</v>
       </c>
       <c r="T50">
-        <v>1.010237805653777</v>
+        <v>1.027892904007554</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.195699063300348</v>
+        <v>2.150888878335034</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5683,22 +5683,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08206520560455663</v>
+        <v>0.08216122072127438</v>
       </c>
       <c r="C51">
-        <v>669.1198527683601</v>
+        <v>648.8792605937415</v>
       </c>
       <c r="D51">
-        <v>1249.97985276836</v>
+        <v>1246.879260593741</v>
       </c>
       <c r="E51">
-        <v>426.26</v>
+        <v>443.4</v>
       </c>
       <c r="F51">
-        <v>839.86</v>
+        <v>857</v>
       </c>
       <c r="G51">
         <v>259</v>
@@ -5719,28 +5719,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M51">
-        <v>63.66138800000001</v>
+        <v>64.9606</v>
       </c>
       <c r="N51">
-        <v>73.26718342857143</v>
+        <v>71.96797142857145</v>
       </c>
       <c r="O51">
-        <v>13.92076485142857</v>
+        <v>13.67391457142858</v>
       </c>
       <c r="P51">
-        <v>59.34641857714286</v>
+        <v>58.29405685714287</v>
       </c>
       <c r="Q51">
-        <v>98.84641857714286</v>
+        <v>97.79405685714286</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1019219325579541</v>
+        <v>0.1029244414425488</v>
       </c>
       <c r="T51">
-        <v>1.027892904007554</v>
+        <v>1.046254206295483</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.150888878335034</v>
+        <v>2.107871100768334</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5765,22 +5765,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08216122072127438</v>
+        <v>0.08225723583799216</v>
       </c>
       <c r="C52">
-        <v>648.8792605937415</v>
+        <v>628.6540124808254</v>
       </c>
       <c r="D52">
-        <v>1246.879260593741</v>
+        <v>1243.794012480825</v>
       </c>
       <c r="E52">
-        <v>443.4</v>
+        <v>460.54</v>
       </c>
       <c r="F52">
-        <v>857</v>
+        <v>874.14</v>
       </c>
       <c r="G52">
         <v>259</v>
@@ -5801,28 +5801,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M52">
-        <v>64.9606</v>
+        <v>66.25981200000001</v>
       </c>
       <c r="N52">
-        <v>71.96797142857145</v>
+        <v>70.66875942857143</v>
       </c>
       <c r="O52">
-        <v>13.67391457142858</v>
+        <v>13.42706429142857</v>
       </c>
       <c r="P52">
-        <v>58.29405685714287</v>
+        <v>57.24169513714286</v>
       </c>
       <c r="Q52">
-        <v>97.79405685714286</v>
+        <v>96.74169513714287</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1029244414425488</v>
+        <v>0.1039678690571268</v>
       </c>
       <c r="T52">
-        <v>1.046254206295483</v>
+        <v>1.065364949493123</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.107871100768334</v>
+        <v>2.066540294870916</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5847,22 +5847,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08225723583799216</v>
+        <v>0.08235325095470991</v>
       </c>
       <c r="C53">
-        <v>628.6540124808254</v>
+        <v>608.4439948098178</v>
       </c>
       <c r="D53">
-        <v>1243.794012480825</v>
+        <v>1240.723994809818</v>
       </c>
       <c r="E53">
-        <v>460.54</v>
+        <v>477.6800000000001</v>
       </c>
       <c r="F53">
-        <v>874.14</v>
+        <v>891.2800000000001</v>
       </c>
       <c r="G53">
         <v>259</v>
@@ -5883,28 +5883,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M53">
-        <v>66.25981200000001</v>
+        <v>67.55902400000001</v>
       </c>
       <c r="N53">
-        <v>70.66875942857143</v>
+        <v>69.36954742857144</v>
       </c>
       <c r="O53">
-        <v>13.42706429142857</v>
+        <v>13.18021401142857</v>
       </c>
       <c r="P53">
-        <v>57.24169513714286</v>
+        <v>56.18933341714286</v>
       </c>
       <c r="Q53">
-        <v>96.74169513714287</v>
+        <v>95.68933341714286</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1039678690571268</v>
+        <v>0.1050547728223123</v>
       </c>
       <c r="T53">
-        <v>1.065364949493123</v>
+        <v>1.085271973657331</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.066540294870916</v>
+        <v>2.026799135354167</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08235325095470991</v>
+        <v>0.08854532607142768</v>
       </c>
       <c r="C54">
-        <v>608.4439948098178</v>
+        <v>420.9261004665764</v>
       </c>
       <c r="D54">
-        <v>1240.723994809818</v>
+        <v>1070.346100466576</v>
       </c>
       <c r="E54">
-        <v>477.6800000000001</v>
+        <v>494.8200000000001</v>
       </c>
       <c r="F54">
-        <v>891.2800000000001</v>
+        <v>908.4200000000001</v>
       </c>
       <c r="G54">
         <v>259</v>
@@ -5965,45 +5965,45 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M54">
-        <v>67.55902400000001</v>
+        <v>81.7578</v>
       </c>
       <c r="N54">
-        <v>69.36954742857144</v>
+        <v>55.17077142857144</v>
       </c>
       <c r="O54">
-        <v>13.18021401142857</v>
+        <v>10.48244657142857</v>
       </c>
       <c r="P54">
-        <v>56.18933341714286</v>
+        <v>44.68832485714287</v>
       </c>
       <c r="Q54">
-        <v>95.68933341714286</v>
+        <v>84.18832485714287</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1050547728223123</v>
+        <v>0.1061879278115483</v>
       </c>
       <c r="T54">
-        <v>1.085271973657331</v>
+        <v>1.106026105232782</v>
       </c>
       <c r="U54">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V54">
         <v>0.19</v>
       </c>
       <c r="W54">
-        <v>0.06139800000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.026799135354167</v>
+        <v>1.674807436459536</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6011,22 +6011,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08854532607142768</v>
+        <v>0.08875636118814545</v>
       </c>
       <c r="C55">
-        <v>420.9261004665764</v>
+        <v>398.8000921069428</v>
       </c>
       <c r="D55">
-        <v>1070.346100466576</v>
+        <v>1065.360092106943</v>
       </c>
       <c r="E55">
-        <v>494.8200000000001</v>
+        <v>511.96</v>
       </c>
       <c r="F55">
-        <v>908.4200000000001</v>
+        <v>925.5600000000001</v>
       </c>
       <c r="G55">
         <v>259</v>
@@ -6047,28 +6047,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M55">
-        <v>81.7578</v>
+        <v>83.3004</v>
       </c>
       <c r="N55">
-        <v>55.17077142857144</v>
+        <v>53.62817142857145</v>
       </c>
       <c r="O55">
-        <v>10.48244657142857</v>
+        <v>10.18935257142858</v>
       </c>
       <c r="P55">
-        <v>44.68832485714287</v>
+        <v>43.43881885714288</v>
       </c>
       <c r="Q55">
-        <v>84.18832485714287</v>
+        <v>82.93881885714288</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1061879278115483</v>
+        <v>0.1073703504090119</v>
       </c>
       <c r="T55">
-        <v>1.106026105232782</v>
+        <v>1.127682590354992</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.674807436459536</v>
+        <v>1.643792483932508</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6093,22 +6093,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08875636118814545</v>
+        <v>0.08896739630486322</v>
       </c>
       <c r="C56">
-        <v>398.8000921069428</v>
+        <v>376.7203211453336</v>
       </c>
       <c r="D56">
-        <v>1065.360092106943</v>
+        <v>1060.420321145334</v>
       </c>
       <c r="E56">
-        <v>511.96</v>
+        <v>529.1</v>
       </c>
       <c r="F56">
-        <v>925.5600000000001</v>
+        <v>942.7</v>
       </c>
       <c r="G56">
         <v>259</v>
@@ -6129,28 +6129,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M56">
-        <v>83.3004</v>
+        <v>84.843</v>
       </c>
       <c r="N56">
-        <v>53.62817142857145</v>
+        <v>52.08557142857144</v>
       </c>
       <c r="O56">
-        <v>10.18935257142858</v>
+        <v>9.896258571428573</v>
       </c>
       <c r="P56">
-        <v>43.43881885714288</v>
+        <v>42.18931285714287</v>
       </c>
       <c r="Q56">
-        <v>82.93881885714288</v>
+        <v>81.68931285714287</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1073703504090119</v>
+        <v>0.1086053251219183</v>
       </c>
       <c r="T56">
-        <v>1.127682590354992</v>
+        <v>1.150301585927078</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -6167,7 +6167,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.643792483932508</v>
+        <v>1.613905347861007</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6175,22 +6175,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08896739630486322</v>
+        <v>0.08917843142158099</v>
       </c>
       <c r="C57">
-        <v>376.7203211453336</v>
+        <v>354.6861473812858</v>
       </c>
       <c r="D57">
-        <v>1060.420321145334</v>
+        <v>1055.526147381286</v>
       </c>
       <c r="E57">
-        <v>529.1</v>
+        <v>546.2400000000001</v>
       </c>
       <c r="F57">
-        <v>942.7</v>
+        <v>959.8400000000001</v>
       </c>
       <c r="G57">
         <v>259</v>
@@ -6211,28 +6211,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M57">
-        <v>84.843</v>
+        <v>86.38560000000001</v>
       </c>
       <c r="N57">
-        <v>52.08557142857144</v>
+        <v>50.54297142857143</v>
       </c>
       <c r="O57">
-        <v>9.896258571428573</v>
+        <v>9.603164571428573</v>
       </c>
       <c r="P57">
-        <v>42.18931285714287</v>
+        <v>40.93980685714286</v>
       </c>
       <c r="Q57">
-        <v>81.68931285714287</v>
+        <v>80.43980685714286</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1086053251219183</v>
+        <v>0.1098964350490477</v>
       </c>
       <c r="T57">
-        <v>1.150301585927078</v>
+        <v>1.173948717661531</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.613905347861007</v>
+        <v>1.585085609506346</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6257,22 +6257,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08917843142158099</v>
+        <v>0.08938946653829875</v>
       </c>
       <c r="C58">
-        <v>354.6861473812858</v>
+        <v>332.6969423789461</v>
       </c>
       <c r="D58">
-        <v>1055.526147381286</v>
+        <v>1050.676942378946</v>
       </c>
       <c r="E58">
-        <v>546.2400000000001</v>
+        <v>563.3800000000001</v>
       </c>
       <c r="F58">
-        <v>959.8400000000001</v>
+        <v>976.9800000000001</v>
       </c>
       <c r="G58">
         <v>259</v>
@@ -6293,28 +6293,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M58">
-        <v>86.38560000000001</v>
+        <v>87.9282</v>
       </c>
       <c r="N58">
-        <v>50.54297142857143</v>
+        <v>49.00037142857144</v>
       </c>
       <c r="O58">
-        <v>9.603164571428573</v>
+        <v>9.310070571428573</v>
       </c>
       <c r="P58">
-        <v>40.93980685714286</v>
+        <v>39.69030085714287</v>
       </c>
       <c r="Q58">
-        <v>80.43980685714286</v>
+        <v>79.19030085714286</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1098964350490477</v>
+        <v>0.1112475966006948</v>
       </c>
       <c r="T58">
-        <v>1.173948717661531</v>
+        <v>1.198695715988285</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.585085609506346</v>
+        <v>1.557277090041323</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6339,22 +6339,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08938946653829875</v>
+        <v>0.08960050165501651</v>
       </c>
       <c r="C59">
-        <v>332.6969423789461</v>
+        <v>310.7520891980666</v>
       </c>
       <c r="D59">
-        <v>1050.676942378946</v>
+        <v>1045.872089198067</v>
       </c>
       <c r="E59">
-        <v>563.3800000000001</v>
+        <v>580.5200000000001</v>
       </c>
       <c r="F59">
-        <v>976.9800000000001</v>
+        <v>994.1200000000001</v>
       </c>
       <c r="G59">
         <v>259</v>
@@ -6375,28 +6375,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M59">
-        <v>87.9282</v>
+        <v>89.47080000000001</v>
       </c>
       <c r="N59">
-        <v>49.00037142857144</v>
+        <v>47.45777142857143</v>
       </c>
       <c r="O59">
-        <v>9.310070571428573</v>
+        <v>9.016976571428572</v>
       </c>
       <c r="P59">
-        <v>39.69030085714287</v>
+        <v>38.44079485714286</v>
       </c>
       <c r="Q59">
-        <v>79.19030085714286</v>
+        <v>77.94079485714286</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1112475966006948</v>
+        <v>0.1126630991786108</v>
       </c>
       <c r="T59">
-        <v>1.198695715988285</v>
+        <v>1.224621142806789</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.557277090041323</v>
+        <v>1.53042748504061</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6421,22 +6421,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08960050165501651</v>
+        <v>0.08981153677173428</v>
       </c>
       <c r="C60">
-        <v>310.7520891980669</v>
+        <v>288.8509821323487</v>
       </c>
       <c r="D60">
-        <v>1045.872089198067</v>
+        <v>1041.110982132349</v>
       </c>
       <c r="E60">
-        <v>580.5199999999999</v>
+        <v>597.66</v>
       </c>
       <c r="F60">
-        <v>994.1199999999999</v>
+        <v>1011.26</v>
       </c>
       <c r="G60">
         <v>259</v>
@@ -6457,28 +6457,28 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M60">
-        <v>89.47079999999998</v>
+        <v>91.01339999999999</v>
       </c>
       <c r="N60">
-        <v>47.45777142857146</v>
+        <v>45.91517142857145</v>
       </c>
       <c r="O60">
-        <v>9.016976571428577</v>
+        <v>8.723882571428577</v>
       </c>
       <c r="P60">
-        <v>38.44079485714288</v>
+        <v>37.19128885714288</v>
       </c>
       <c r="Q60">
-        <v>77.94079485714289</v>
+        <v>76.69128885714288</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1126630991786107</v>
+        <v>0.1141476506627665</v>
       </c>
       <c r="T60">
-        <v>1.224621142806788</v>
+        <v>1.251811224592049</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.530427485040611</v>
+        <v>1.504488036141617</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6503,22 +6503,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08981153677173428</v>
+        <v>0.1195184061597707</v>
       </c>
       <c r="C61">
-        <v>288.8509821323487</v>
+        <v>-134.8909016025104</v>
       </c>
       <c r="D61">
-        <v>1041.110982132349</v>
+        <v>634.5090983974894</v>
       </c>
       <c r="E61">
-        <v>597.66</v>
+        <v>614.7999999999998</v>
       </c>
       <c r="F61">
-        <v>1011.26</v>
+        <v>1028.4</v>
       </c>
       <c r="G61">
         <v>259</v>
@@ -6539,45 +6539,45 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M61">
-        <v>91.01339999999999</v>
+        <v>150.96912</v>
       </c>
       <c r="N61">
-        <v>45.91517142857145</v>
+        <v>-14.04054857142856</v>
       </c>
       <c r="O61">
-        <v>8.723882571428577</v>
+        <v>-2.667704228571426</v>
       </c>
       <c r="P61">
-        <v>37.19128885714288</v>
+        <v>-11.37284434285713</v>
       </c>
       <c r="Q61">
-        <v>76.69128885714288</v>
+        <v>28.12715565714287</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1141476506627665</v>
+        <v>0.1165429648910088</v>
       </c>
       <c r="T61">
-        <v>1.251811224592049</v>
+        <v>1.295682245881917</v>
       </c>
       <c r="U61">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.19</v>
+        <v>0.172329470897284</v>
       </c>
       <c r="W61">
-        <v>0.07290000000000001</v>
+        <v>0.1215020336722787</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y61">
-        <v>1.504488036141617</v>
+        <v>0.9069972152488631</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6585,22 +6585,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1195184061597707</v>
+        <v>0.1205284061597708</v>
       </c>
       <c r="C62">
-        <v>-134.8909016025104</v>
+        <v>-160.3455910185318</v>
       </c>
       <c r="D62">
-        <v>634.5090983974894</v>
+        <v>626.1944089814682</v>
       </c>
       <c r="E62">
-        <v>614.7999999999998</v>
+        <v>631.9399999999999</v>
       </c>
       <c r="F62">
-        <v>1028.4</v>
+        <v>1045.54</v>
       </c>
       <c r="G62">
         <v>259</v>
@@ -6621,37 +6621,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M62">
-        <v>150.96912</v>
+        <v>153.485272</v>
       </c>
       <c r="N62">
-        <v>-14.04054857142856</v>
+        <v>-16.55670057142856</v>
       </c>
       <c r="O62">
-        <v>-2.667704228571426</v>
+        <v>-3.145773108571427</v>
       </c>
       <c r="P62">
-        <v>-11.37284434285713</v>
+        <v>-13.41092746285714</v>
       </c>
       <c r="Q62">
-        <v>28.12715565714287</v>
+        <v>26.08907253714286</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1165429648910088</v>
+        <v>0.1183568870677013</v>
       </c>
       <c r="T62">
-        <v>1.295682245881917</v>
+        <v>1.328904867571197</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.172329470897284</v>
+        <v>0.1695043976038859</v>
       </c>
       <c r="W62">
-        <v>0.1215020336722787</v>
+        <v>0.1219167544317496</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.9069972152488631</v>
+        <v>0.8921284084415047</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6667,22 +6667,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1205284061597708</v>
+        <v>0.1215384061597707</v>
       </c>
       <c r="C63">
-        <v>-160.3455910185318</v>
+        <v>-185.5851855317334</v>
       </c>
       <c r="D63">
-        <v>626.1944089814682</v>
+        <v>618.0948144682667</v>
       </c>
       <c r="E63">
-        <v>631.9399999999999</v>
+        <v>649.08</v>
       </c>
       <c r="F63">
-        <v>1045.54</v>
+        <v>1062.68</v>
       </c>
       <c r="G63">
         <v>259</v>
@@ -6703,37 +6703,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M63">
-        <v>153.485272</v>
+        <v>156.001424</v>
       </c>
       <c r="N63">
-        <v>-16.55670057142856</v>
+        <v>-19.07285257142857</v>
       </c>
       <c r="O63">
-        <v>-3.145773108571427</v>
+        <v>-3.623841988571428</v>
       </c>
       <c r="P63">
-        <v>-13.41092746285714</v>
+        <v>-15.44901058285714</v>
       </c>
       <c r="Q63">
-        <v>26.08907253714286</v>
+        <v>24.05098941714286</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1183568870677013</v>
+        <v>0.1202662788326408</v>
       </c>
       <c r="T63">
-        <v>1.328904867571197</v>
+        <v>1.363876048296754</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1695043976038859</v>
+        <v>0.166770455707049</v>
       </c>
       <c r="W63">
-        <v>0.1219167544317496</v>
+        <v>0.1223180971022052</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8921284084415047</v>
+        <v>0.8777392405634158</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6749,22 +6749,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1215384061597707</v>
+        <v>0.1225484061597708</v>
       </c>
       <c r="C64">
-        <v>-185.5851855317334</v>
+        <v>-210.6179250820416</v>
       </c>
       <c r="D64">
-        <v>618.0948144682667</v>
+        <v>610.2020749179584</v>
       </c>
       <c r="E64">
-        <v>649.08</v>
+        <v>666.2199999999999</v>
       </c>
       <c r="F64">
-        <v>1062.68</v>
+        <v>1079.82</v>
       </c>
       <c r="G64">
         <v>259</v>
@@ -6785,37 +6785,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M64">
-        <v>156.001424</v>
+        <v>158.517576</v>
       </c>
       <c r="N64">
-        <v>-19.07285257142857</v>
+        <v>-21.58900457142857</v>
       </c>
       <c r="O64">
-        <v>-3.623841988571428</v>
+        <v>-4.101910868571429</v>
       </c>
       <c r="P64">
-        <v>-15.44901058285714</v>
+        <v>-17.48709370285714</v>
       </c>
       <c r="Q64">
-        <v>24.05098941714286</v>
+        <v>22.01290629714286</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1202662788326408</v>
+        <v>0.1222788809632528</v>
       </c>
       <c r="T64">
-        <v>1.363876048296754</v>
+        <v>1.400737563115586</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.166770455707049</v>
+        <v>0.1641233056164609</v>
       </c>
       <c r="W64">
-        <v>0.1223180971022052</v>
+        <v>0.1227066987355035</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8777392405634158</v>
+        <v>0.8638068716655838</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6831,22 +6831,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1225484061597708</v>
+        <v>0.1235584061597708</v>
       </c>
       <c r="C65">
-        <v>-210.6179250820416</v>
+        <v>-235.4516340375428</v>
       </c>
       <c r="D65">
-        <v>610.2020749179584</v>
+        <v>602.5083659624572</v>
       </c>
       <c r="E65">
-        <v>666.2199999999999</v>
+        <v>683.36</v>
       </c>
       <c r="F65">
-        <v>1079.82</v>
+        <v>1096.96</v>
       </c>
       <c r="G65">
         <v>259</v>
@@ -6867,37 +6867,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M65">
-        <v>158.517576</v>
+        <v>161.033728</v>
       </c>
       <c r="N65">
-        <v>-21.58900457142857</v>
+        <v>-24.10515657142858</v>
       </c>
       <c r="O65">
-        <v>-4.101910868571429</v>
+        <v>-4.57997974857143</v>
       </c>
       <c r="P65">
-        <v>-17.48709370285714</v>
+        <v>-19.52517682285715</v>
       </c>
       <c r="Q65">
-        <v>22.01290629714286</v>
+        <v>19.97482317714285</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1222788809632528</v>
+        <v>0.1244032943233431</v>
       </c>
       <c r="T65">
-        <v>1.400737563115586</v>
+        <v>1.439646939868797</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1641233056164609</v>
+        <v>0.1615588789662037</v>
       </c>
       <c r="W65">
-        <v>0.1227066987355035</v>
+        <v>0.1230831565677613</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8638068716655838</v>
+        <v>0.850309889295809</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6913,22 +6913,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1235584061597708</v>
+        <v>0.1245684061597708</v>
       </c>
       <c r="C66">
-        <v>-235.4516340375428</v>
+        <v>-260.0937470668804</v>
       </c>
       <c r="D66">
-        <v>602.5083659624572</v>
+        <v>595.0062529331198</v>
       </c>
       <c r="E66">
-        <v>683.36</v>
+        <v>700.5000000000001</v>
       </c>
       <c r="F66">
-        <v>1096.96</v>
+        <v>1114.1</v>
       </c>
       <c r="G66">
         <v>259</v>
@@ -6949,37 +6949,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M66">
-        <v>161.033728</v>
+        <v>163.54988</v>
       </c>
       <c r="N66">
-        <v>-24.10515657142858</v>
+        <v>-26.62130857142859</v>
       </c>
       <c r="O66">
-        <v>-4.57997974857143</v>
+        <v>-5.058048628571432</v>
       </c>
       <c r="P66">
-        <v>-19.52517682285715</v>
+        <v>-21.56325994285715</v>
       </c>
       <c r="Q66">
-        <v>19.97482317714285</v>
+        <v>17.93674005714285</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1244032943233431</v>
+        <v>0.1266491027325815</v>
       </c>
       <c r="T66">
-        <v>1.439646939868797</v>
+        <v>1.480779709579334</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.1615588789662037</v>
+        <v>0.159073357751339</v>
       </c>
       <c r="W66">
-        <v>0.1230831565677613</v>
+        <v>0.1234480310821034</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.850309889295809</v>
+        <v>0.8372281986912581</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6995,22 +6995,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1245684061597708</v>
+        <v>0.1255784061597708</v>
       </c>
       <c r="C67">
-        <v>-260.0937470668804</v>
+        <v>-284.551333102524</v>
       </c>
       <c r="D67">
-        <v>595.0062529331198</v>
+        <v>587.688666897476</v>
       </c>
       <c r="E67">
-        <v>700.5000000000001</v>
+        <v>717.64</v>
       </c>
       <c r="F67">
-        <v>1114.1</v>
+        <v>1131.24</v>
       </c>
       <c r="G67">
         <v>259</v>
@@ -7031,37 +7031,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M67">
-        <v>163.54988</v>
+        <v>166.066032</v>
       </c>
       <c r="N67">
-        <v>-26.62130857142859</v>
+        <v>-29.13746057142856</v>
       </c>
       <c r="O67">
-        <v>-5.058048628571432</v>
+        <v>-5.536117508571427</v>
       </c>
       <c r="P67">
-        <v>-21.56325994285715</v>
+        <v>-23.60134306285714</v>
       </c>
       <c r="Q67">
-        <v>17.93674005714285</v>
+        <v>15.89865693714286</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1266491027325815</v>
+        <v>0.1290270175188339</v>
       </c>
       <c r="T67">
-        <v>1.480779709579334</v>
+        <v>1.524332053978726</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.159073357751339</v>
+        <v>0.1566631553611673</v>
       </c>
       <c r="W67">
-        <v>0.1234480310821034</v>
+        <v>0.1238018487929807</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8372281986912581</v>
+        <v>0.8245429229535119</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7077,22 +7077,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1255784061597708</v>
+        <v>0.1265884061597707</v>
       </c>
       <c r="C68">
-        <v>-284.551333102524</v>
+        <v>-308.8311175572751</v>
       </c>
       <c r="D68">
-        <v>587.688666897476</v>
+        <v>580.548882442725</v>
       </c>
       <c r="E68">
-        <v>717.64</v>
+        <v>734.7800000000001</v>
       </c>
       <c r="F68">
-        <v>1131.24</v>
+        <v>1148.38</v>
       </c>
       <c r="G68">
         <v>259</v>
@@ -7113,37 +7113,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M68">
-        <v>166.066032</v>
+        <v>168.582184</v>
       </c>
       <c r="N68">
-        <v>-29.13746057142856</v>
+        <v>-31.6536125714286</v>
       </c>
       <c r="O68">
-        <v>-5.536117508571427</v>
+        <v>-6.014186388571433</v>
       </c>
       <c r="P68">
-        <v>-23.60134306285714</v>
+        <v>-25.63942618285716</v>
       </c>
       <c r="Q68">
-        <v>15.89865693714286</v>
+        <v>13.86057381714284</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1290270175188339</v>
+        <v>0.131549048352738</v>
       </c>
       <c r="T68">
-        <v>1.524332053978726</v>
+        <v>1.570523934402324</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.1566631553611673</v>
+        <v>0.1543248993110006</v>
       </c>
       <c r="W68">
-        <v>0.1238018487929807</v>
+        <v>0.1241451047811451</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8245429229535119</v>
+        <v>0.8122363121631608</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7159,22 +7159,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1265884061597707</v>
+        <v>0.1275984061597708</v>
       </c>
       <c r="C69">
-        <v>-308.8311175572751</v>
+        <v>-332.9395029407666</v>
       </c>
       <c r="D69">
-        <v>580.548882442725</v>
+        <v>573.5804970592334</v>
       </c>
       <c r="E69">
-        <v>734.7800000000001</v>
+        <v>751.92</v>
       </c>
       <c r="F69">
-        <v>1148.38</v>
+        <v>1165.52</v>
       </c>
       <c r="G69">
         <v>259</v>
@@ -7195,37 +7195,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M69">
-        <v>168.582184</v>
+        <v>171.098336</v>
       </c>
       <c r="N69">
-        <v>-31.6536125714286</v>
+        <v>-34.16976457142857</v>
       </c>
       <c r="O69">
-        <v>-6.014186388571433</v>
+        <v>-6.492255268571429</v>
       </c>
       <c r="P69">
-        <v>-25.63942618285716</v>
+        <v>-27.67750930285714</v>
       </c>
       <c r="Q69">
-        <v>13.86057381714284</v>
+        <v>11.82249069714286</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.131549048352738</v>
+        <v>0.134228706113761</v>
       </c>
       <c r="T69">
-        <v>1.570523934402324</v>
+        <v>1.619602807352396</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.1543248993110006</v>
+        <v>0.1520554154976035</v>
       </c>
       <c r="W69">
-        <v>0.1241451047811451</v>
+        <v>0.1244782650049518</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8122363121631608</v>
+        <v>0.8002916605137027</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7241,22 +7241,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1275984061597708</v>
+        <v>0.1667459811705529</v>
       </c>
       <c r="C70">
-        <v>-332.9395029407666</v>
+        <v>-532.2015522640788</v>
       </c>
       <c r="D70">
-        <v>573.5804970592334</v>
+        <v>391.4584477359213</v>
       </c>
       <c r="E70">
-        <v>751.92</v>
+        <v>769.0600000000001</v>
       </c>
       <c r="F70">
-        <v>1165.52</v>
+        <v>1182.66</v>
       </c>
       <c r="G70">
         <v>259</v>
@@ -7277,45 +7277,45 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M70">
-        <v>171.098336</v>
+        <v>237.478128</v>
       </c>
       <c r="N70">
-        <v>-34.16976457142857</v>
+        <v>-100.5495565714286</v>
       </c>
       <c r="O70">
-        <v>-6.492255268571429</v>
+        <v>-19.10441574857143</v>
       </c>
       <c r="P70">
-        <v>-27.67750930285714</v>
+        <v>-81.44514082285716</v>
       </c>
       <c r="Q70">
-        <v>11.82249069714286</v>
+        <v>-41.94514082285716</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.134228706113761</v>
+        <v>0.1399121321522119</v>
       </c>
       <c r="T70">
-        <v>1.619602807352396</v>
+        <v>1.723696751183406</v>
       </c>
       <c r="U70">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1520554154976035</v>
+        <v>0.1095529461619664</v>
       </c>
       <c r="W70">
-        <v>0.1244782650049518</v>
+        <v>0.1788017684106772</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.8002916605137027</v>
+        <v>0.5765944534840338</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7323,22 +7323,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1667459811705529</v>
+        <v>0.1682959811705529</v>
       </c>
       <c r="C71">
-        <v>-532.2015522640788</v>
+        <v>-554.2017602873476</v>
       </c>
       <c r="D71">
-        <v>391.4584477359213</v>
+        <v>386.5982397126526</v>
       </c>
       <c r="E71">
-        <v>769.0600000000001</v>
+        <v>786.2000000000002</v>
       </c>
       <c r="F71">
-        <v>1182.66</v>
+        <v>1199.8</v>
       </c>
       <c r="G71">
         <v>259</v>
@@ -7359,37 +7359,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M71">
-        <v>237.478128</v>
+        <v>240.9198400000001</v>
       </c>
       <c r="N71">
-        <v>-100.5495565714286</v>
+        <v>-103.9912685714286</v>
       </c>
       <c r="O71">
-        <v>-19.10441574857143</v>
+        <v>-19.75834102857144</v>
       </c>
       <c r="P71">
-        <v>-81.44514082285716</v>
+        <v>-84.23292754285717</v>
       </c>
       <c r="Q71">
-        <v>-41.94514082285716</v>
+        <v>-44.73292754285717</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1399121321522119</v>
+        <v>0.1430492032239523</v>
       </c>
       <c r="T71">
-        <v>1.723696751183406</v>
+        <v>1.781153309556186</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1095529461619664</v>
+        <v>0.1079879040739383</v>
       </c>
       <c r="W71">
-        <v>0.1788017684106772</v>
+        <v>0.1791160288619532</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5765944534840338</v>
+        <v>0.5683573898628334</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7405,22 +7405,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1682959811705529</v>
+        <v>0.1698459811705529</v>
       </c>
       <c r="C72">
-        <v>-554.2017602873476</v>
+        <v>-576.0827631120407</v>
       </c>
       <c r="D72">
-        <v>386.5982397126526</v>
+        <v>381.8572368879594</v>
       </c>
       <c r="E72">
-        <v>786.2000000000002</v>
+        <v>803.34</v>
       </c>
       <c r="F72">
-        <v>1199.8</v>
+        <v>1216.94</v>
       </c>
       <c r="G72">
         <v>259</v>
@@ -7441,37 +7441,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M72">
-        <v>240.9198400000001</v>
+        <v>244.361552</v>
       </c>
       <c r="N72">
-        <v>-103.9912685714286</v>
+        <v>-107.4329805714286</v>
       </c>
       <c r="O72">
-        <v>-19.75834102857144</v>
+        <v>-20.41226630857143</v>
       </c>
       <c r="P72">
-        <v>-84.23292754285717</v>
+        <v>-87.02071426285714</v>
       </c>
       <c r="Q72">
-        <v>-44.73292754285717</v>
+        <v>-47.52071426285714</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1430492032239523</v>
+        <v>0.1464026240247782</v>
       </c>
       <c r="T72">
-        <v>1.781153309556186</v>
+        <v>1.842572389196055</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1079879040739383</v>
+        <v>0.1064669476785308</v>
       </c>
       <c r="W72">
-        <v>0.1791160288619532</v>
+        <v>0.179421436906151</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5683573898628334</v>
+        <v>0.5603523562027934</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7487,22 +7487,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1698459811705529</v>
+        <v>0.1713959811705529</v>
       </c>
       <c r="C73">
-        <v>-576.0827631120403</v>
+        <v>-597.8488931852152</v>
       </c>
       <c r="D73">
-        <v>381.8572368879595</v>
+        <v>377.2311068147848</v>
       </c>
       <c r="E73">
-        <v>803.3399999999998</v>
+        <v>820.4799999999999</v>
       </c>
       <c r="F73">
-        <v>1216.94</v>
+        <v>1234.08</v>
       </c>
       <c r="G73">
         <v>259</v>
@@ -7523,37 +7523,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M73">
-        <v>244.361552</v>
+        <v>247.803264</v>
       </c>
       <c r="N73">
-        <v>-107.4329805714285</v>
+        <v>-110.8746925714285</v>
       </c>
       <c r="O73">
-        <v>-20.41226630857142</v>
+        <v>-21.06619158857142</v>
       </c>
       <c r="P73">
-        <v>-87.0207142628571</v>
+        <v>-89.80850098285711</v>
       </c>
       <c r="Q73">
-        <v>-47.5207142628571</v>
+        <v>-50.30850098285711</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1464026240247782</v>
+        <v>0.149995574882806</v>
       </c>
       <c r="T73">
-        <v>1.842572389196054</v>
+        <v>1.908378545953056</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1064669476785308</v>
+        <v>0.1049882400718845</v>
       </c>
       <c r="W73">
-        <v>0.179421436906151</v>
+        <v>0.1797183613935656</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5603523562027937</v>
+        <v>0.5525696845888659</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7569,22 +7569,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1713959811705529</v>
+        <v>0.1729459811705529</v>
       </c>
       <c r="C74">
-        <v>-597.8488931852152</v>
+        <v>-619.5042755197628</v>
       </c>
       <c r="D74">
-        <v>377.2311068147848</v>
+        <v>372.7157244802372</v>
       </c>
       <c r="E74">
-        <v>820.4799999999999</v>
+        <v>837.62</v>
       </c>
       <c r="F74">
-        <v>1234.08</v>
+        <v>1251.22</v>
       </c>
       <c r="G74">
         <v>259</v>
@@ -7605,37 +7605,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M74">
-        <v>247.803264</v>
+        <v>251.244976</v>
       </c>
       <c r="N74">
-        <v>-110.8746925714285</v>
+        <v>-114.3164045714286</v>
       </c>
       <c r="O74">
-        <v>-21.06619158857142</v>
+        <v>-21.72011686857143</v>
       </c>
       <c r="P74">
-        <v>-89.80850098285711</v>
+        <v>-92.59628770285714</v>
       </c>
       <c r="Q74">
-        <v>-50.30850098285711</v>
+        <v>-53.09628770285714</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.149995574882806</v>
+        <v>0.1538546702488358</v>
       </c>
       <c r="T74">
-        <v>1.908378545953056</v>
+        <v>1.979059232840207</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1049882400718845</v>
+        <v>0.1035500450024066</v>
       </c>
       <c r="W74">
-        <v>0.1797183613935656</v>
+        <v>0.1800071509635168</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5525696845888659</v>
+        <v>0.5450002368547717</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7651,22 +7651,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1729459811705529</v>
+        <v>0.1744959811705529</v>
       </c>
       <c r="C75">
-        <v>-619.5042755197628</v>
+        <v>-641.0528399622975</v>
       </c>
       <c r="D75">
-        <v>372.7157244802372</v>
+        <v>368.3071600377024</v>
       </c>
       <c r="E75">
-        <v>837.62</v>
+        <v>854.7599999999999</v>
       </c>
       <c r="F75">
-        <v>1251.22</v>
+        <v>1268.36</v>
       </c>
       <c r="G75">
         <v>259</v>
@@ -7687,37 +7687,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M75">
-        <v>251.244976</v>
+        <v>254.686688</v>
       </c>
       <c r="N75">
-        <v>-114.3164045714286</v>
+        <v>-117.7581165714285</v>
       </c>
       <c r="O75">
-        <v>-21.72011686857143</v>
+        <v>-22.37404214857142</v>
       </c>
       <c r="P75">
-        <v>-92.59628770285714</v>
+        <v>-95.38407442285711</v>
       </c>
       <c r="Q75">
-        <v>-53.09628770285714</v>
+        <v>-55.88407442285711</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1538546702488358</v>
+        <v>0.1580106191045603</v>
       </c>
       <c r="T75">
-        <v>1.979059232840207</v>
+        <v>2.055176895641753</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1035500450024066</v>
+        <v>0.1021507200699417</v>
       </c>
       <c r="W75">
-        <v>0.1800071509635168</v>
+        <v>0.1802881354099557</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5450002368547717</v>
+        <v>0.5376353687891668</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7733,22 +7733,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1744959811705529</v>
+        <v>0.1760459811705529</v>
       </c>
       <c r="C76">
-        <v>-641.0528399622975</v>
+        <v>-662.4983326005764</v>
       </c>
       <c r="D76">
-        <v>368.3071600377024</v>
+        <v>364.0016673994236</v>
       </c>
       <c r="E76">
-        <v>854.7599999999999</v>
+        <v>871.9</v>
       </c>
       <c r="F76">
-        <v>1268.36</v>
+        <v>1285.5</v>
       </c>
       <c r="G76">
         <v>259</v>
@@ -7769,37 +7769,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M76">
-        <v>254.686688</v>
+        <v>258.1284</v>
       </c>
       <c r="N76">
-        <v>-117.7581165714285</v>
+        <v>-121.1998285714286</v>
       </c>
       <c r="O76">
-        <v>-22.37404214857142</v>
+        <v>-23.02796742857143</v>
       </c>
       <c r="P76">
-        <v>-95.38407442285711</v>
+        <v>-98.17186114285713</v>
       </c>
       <c r="Q76">
-        <v>-55.88407442285711</v>
+        <v>-58.67186114285713</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1580106191045603</v>
+        <v>0.1624990438687427</v>
       </c>
       <c r="T76">
-        <v>2.055176895641753</v>
+        <v>2.137383971467424</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1021507200699417</v>
+        <v>0.1007887104690091</v>
       </c>
       <c r="W76">
-        <v>0.1802881354099557</v>
+        <v>0.180561626937823</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5376353687891668</v>
+        <v>0.5304668972053111</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7815,22 +7815,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1760459811705529</v>
+        <v>0.1775959811705529</v>
       </c>
       <c r="C77">
-        <v>-662.4983326005764</v>
+        <v>-683.8443263800532</v>
       </c>
       <c r="D77">
-        <v>364.0016673994236</v>
+        <v>359.7956736199469</v>
       </c>
       <c r="E77">
-        <v>871.9</v>
+        <v>889.0400000000001</v>
       </c>
       <c r="F77">
-        <v>1285.5</v>
+        <v>1302.64</v>
       </c>
       <c r="G77">
         <v>259</v>
@@ -7851,37 +7851,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M77">
-        <v>258.1284</v>
+        <v>261.5701120000001</v>
       </c>
       <c r="N77">
-        <v>-121.1998285714286</v>
+        <v>-124.6415405714286</v>
       </c>
       <c r="O77">
-        <v>-23.02796742857143</v>
+        <v>-23.68189270857144</v>
       </c>
       <c r="P77">
-        <v>-98.17186114285713</v>
+        <v>-100.9596478628572</v>
       </c>
       <c r="Q77">
-        <v>-58.67186114285713</v>
+        <v>-61.45964786285717</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1624990438687427</v>
+        <v>0.1673615040299404</v>
       </c>
       <c r="T77">
-        <v>2.137383971467424</v>
+        <v>2.226441636945233</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1007887104690091</v>
+        <v>0.09946254322599583</v>
       </c>
       <c r="W77">
-        <v>0.180561626937823</v>
+        <v>0.18082792132022</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5304668972053111</v>
+        <v>0.5234870696105043</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7897,22 +7897,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1775959811705529</v>
+        <v>0.1791459811705529</v>
       </c>
       <c r="C78">
-        <v>-683.8443263800532</v>
+        <v>-705.0942309928005</v>
       </c>
       <c r="D78">
-        <v>359.7956736199469</v>
+        <v>355.6857690071995</v>
       </c>
       <c r="E78">
-        <v>889.0400000000001</v>
+        <v>906.1799999999999</v>
       </c>
       <c r="F78">
-        <v>1302.64</v>
+        <v>1319.78</v>
       </c>
       <c r="G78">
         <v>259</v>
@@ -7933,37 +7933,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M78">
-        <v>261.5701120000001</v>
+        <v>265.011824</v>
       </c>
       <c r="N78">
-        <v>-124.6415405714286</v>
+        <v>-128.0832525714285</v>
       </c>
       <c r="O78">
-        <v>-23.68189270857144</v>
+        <v>-24.33581798857142</v>
       </c>
       <c r="P78">
-        <v>-100.9596478628572</v>
+        <v>-103.7474345828571</v>
       </c>
       <c r="Q78">
-        <v>-61.45964786285717</v>
+        <v>-64.24743458285712</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1673615040299404</v>
+        <v>0.1726467868138508</v>
       </c>
       <c r="T78">
-        <v>2.226441636945233</v>
+        <v>2.3232434472472</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.09946254322599583</v>
+        <v>0.09817082188539851</v>
       </c>
       <c r="W78">
-        <v>0.18082792132022</v>
+        <v>0.181087298965412</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5234870696105043</v>
+        <v>0.5166885362389395</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7979,22 +7979,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1791459811705529</v>
+        <v>0.1806959811705529</v>
       </c>
       <c r="C79">
-        <v>-705.0942309928005</v>
+        <v>-726.2513020963287</v>
       </c>
       <c r="D79">
-        <v>355.6857690071995</v>
+        <v>351.6686979036714</v>
       </c>
       <c r="E79">
-        <v>906.1799999999999</v>
+        <v>923.3200000000001</v>
       </c>
       <c r="F79">
-        <v>1319.78</v>
+        <v>1336.92</v>
       </c>
       <c r="G79">
         <v>259</v>
@@ -8015,37 +8015,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M79">
-        <v>265.011824</v>
+        <v>268.453536</v>
       </c>
       <c r="N79">
-        <v>-128.0832525714285</v>
+        <v>-131.5249645714286</v>
       </c>
       <c r="O79">
-        <v>-24.33581798857142</v>
+        <v>-24.98974326857143</v>
       </c>
       <c r="P79">
-        <v>-103.7474345828571</v>
+        <v>-106.5352213028572</v>
       </c>
       <c r="Q79">
-        <v>-64.24743458285712</v>
+        <v>-67.03522130285717</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1726467868138508</v>
+        <v>0.178412549850844</v>
       </c>
       <c r="T79">
-        <v>2.3232434472472</v>
+        <v>2.428845422122072</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.09817082188539851</v>
+        <v>0.09691222160481644</v>
       </c>
       <c r="W79">
-        <v>0.181087298965412</v>
+        <v>0.1813400259017529</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5166885362389395</v>
+        <v>0.510064324235876</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8061,22 +8061,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1806959811705529</v>
+        <v>0.1822459811705529</v>
       </c>
       <c r="C80">
-        <v>-726.2513020963287</v>
+        <v>-747.3186499146818</v>
       </c>
       <c r="D80">
-        <v>351.6686979036714</v>
+        <v>347.7413500853183</v>
       </c>
       <c r="E80">
-        <v>923.3200000000001</v>
+        <v>940.4600000000002</v>
       </c>
       <c r="F80">
-        <v>1336.92</v>
+        <v>1354.06</v>
       </c>
       <c r="G80">
         <v>259</v>
@@ -8097,37 +8097,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M80">
-        <v>268.453536</v>
+        <v>271.895248</v>
       </c>
       <c r="N80">
-        <v>-131.5249645714286</v>
+        <v>-134.9666765714286</v>
       </c>
       <c r="O80">
-        <v>-24.98974326857143</v>
+        <v>-25.64366854857143</v>
       </c>
       <c r="P80">
-        <v>-106.5352213028572</v>
+        <v>-109.3230080228572</v>
       </c>
       <c r="Q80">
-        <v>-67.03522130285717</v>
+        <v>-69.82300802285715</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.178412549850844</v>
+        <v>0.1847274331770747</v>
       </c>
       <c r="T80">
-        <v>2.428845422122072</v>
+        <v>2.544504727937409</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.09691222160481644</v>
+        <v>0.095685484622477</v>
       </c>
       <c r="W80">
-        <v>0.1813400259017529</v>
+        <v>0.1815863546878066</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.510064324235876</v>
+        <v>0.5036078138025105</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8143,22 +8143,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1822459811705529</v>
+        <v>0.2121500932873341</v>
       </c>
       <c r="C81">
-        <v>-747.3186499146818</v>
+        <v>-826.1012356993866</v>
       </c>
       <c r="D81">
-        <v>347.7413500853183</v>
+        <v>286.0987643006134</v>
       </c>
       <c r="E81">
-        <v>940.4600000000002</v>
+        <v>957.6</v>
       </c>
       <c r="F81">
-        <v>1354.06</v>
+        <v>1371.2</v>
       </c>
       <c r="G81">
         <v>259</v>
@@ -8179,45 +8179,45 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M81">
-        <v>271.895248</v>
+        <v>323.3289600000001</v>
       </c>
       <c r="N81">
-        <v>-134.9666765714286</v>
+        <v>-186.4003885714286</v>
       </c>
       <c r="O81">
-        <v>-25.64366854857143</v>
+        <v>-35.41607382857143</v>
       </c>
       <c r="P81">
-        <v>-109.3230080228572</v>
+        <v>-150.9843147428572</v>
       </c>
       <c r="Q81">
-        <v>-69.82300802285715</v>
+        <v>-111.4843147428572</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1847274331770747</v>
+        <v>0.1934443654198345</v>
       </c>
       <c r="T81">
-        <v>2.544504727937409</v>
+        <v>2.704158403223714</v>
       </c>
       <c r="U81">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.095685484622477</v>
+        <v>0.08046426949020766</v>
       </c>
       <c r="W81">
-        <v>0.1815863546878066</v>
+        <v>0.216826525254209</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.5036078138025105</v>
+        <v>0.4234961552116192</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8225,22 +8225,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2121500932873341</v>
+        <v>0.2140500932873342</v>
       </c>
       <c r="C82">
-        <v>-826.1012356993866</v>
+        <v>-846.4276272520231</v>
       </c>
       <c r="D82">
-        <v>286.0987643006134</v>
+        <v>282.9123727479771</v>
       </c>
       <c r="E82">
-        <v>957.6</v>
+        <v>974.7400000000001</v>
       </c>
       <c r="F82">
-        <v>1371.2</v>
+        <v>1388.34</v>
       </c>
       <c r="G82">
         <v>259</v>
@@ -8261,37 +8261,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M82">
-        <v>323.3289600000001</v>
+        <v>327.370572</v>
       </c>
       <c r="N82">
-        <v>-186.4003885714286</v>
+        <v>-190.4420005714286</v>
       </c>
       <c r="O82">
-        <v>-35.41607382857143</v>
+        <v>-36.18398010857143</v>
       </c>
       <c r="P82">
-        <v>-150.9843147428572</v>
+        <v>-154.2580204628572</v>
       </c>
       <c r="Q82">
-        <v>-111.4843147428572</v>
+        <v>-114.7580204628572</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1934443654198345</v>
+        <v>0.2012151214945627</v>
       </c>
       <c r="T82">
-        <v>2.704158403223714</v>
+        <v>2.846482529709173</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08046426949020766</v>
+        <v>0.07947088344711868</v>
       </c>
       <c r="W82">
-        <v>0.216826525254209</v>
+        <v>0.2170607656831694</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4234961552116192</v>
+        <v>0.418267807616414</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8307,22 +8307,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2140500932873342</v>
+        <v>0.2159500932873342</v>
       </c>
       <c r="C83">
-        <v>-846.4276272520231</v>
+        <v>-866.6838244588985</v>
       </c>
       <c r="D83">
-        <v>282.9123727479771</v>
+        <v>279.7961755411016</v>
       </c>
       <c r="E83">
-        <v>974.7400000000001</v>
+        <v>991.88</v>
       </c>
       <c r="F83">
-        <v>1388.34</v>
+        <v>1405.48</v>
       </c>
       <c r="G83">
         <v>259</v>
@@ -8343,37 +8343,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M83">
-        <v>327.370572</v>
+        <v>331.412184</v>
       </c>
       <c r="N83">
-        <v>-190.4420005714286</v>
+        <v>-194.4836125714286</v>
       </c>
       <c r="O83">
-        <v>-36.18398010857143</v>
+        <v>-36.95188638857143</v>
       </c>
       <c r="P83">
-        <v>-154.2580204628572</v>
+        <v>-157.5317261828571</v>
       </c>
       <c r="Q83">
-        <v>-114.7580204628572</v>
+        <v>-118.0317261828571</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2012151214945627</v>
+        <v>0.2098492949109273</v>
       </c>
       <c r="T83">
-        <v>2.846482529709173</v>
+        <v>3.004620448026349</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07947088344711868</v>
+        <v>0.07850172633190991</v>
       </c>
       <c r="W83">
-        <v>0.2170607656831694</v>
+        <v>0.2172892929309357</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.418267807616414</v>
+        <v>0.4131669806942627</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8389,22 +8389,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2159500932873342</v>
+        <v>0.2178500932873342</v>
       </c>
       <c r="C84">
-        <v>-866.6838244588985</v>
+        <v>-886.872121560315</v>
       </c>
       <c r="D84">
-        <v>279.7961755411016</v>
+        <v>276.7478784396852</v>
       </c>
       <c r="E84">
-        <v>991.88</v>
+        <v>1009.02</v>
       </c>
       <c r="F84">
-        <v>1405.48</v>
+        <v>1422.62</v>
       </c>
       <c r="G84">
         <v>259</v>
@@ -8425,37 +8425,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M84">
-        <v>331.412184</v>
+        <v>335.4537960000001</v>
       </c>
       <c r="N84">
-        <v>-194.4836125714286</v>
+        <v>-198.5252245714286</v>
       </c>
       <c r="O84">
-        <v>-36.95188638857143</v>
+        <v>-37.71979266857144</v>
       </c>
       <c r="P84">
-        <v>-157.5317261828571</v>
+        <v>-160.8054319028572</v>
       </c>
       <c r="Q84">
-        <v>-118.0317261828571</v>
+        <v>-121.3054319028572</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2098492949109273</v>
+        <v>0.2194992534350995</v>
       </c>
       <c r="T84">
-        <v>3.004620448026349</v>
+        <v>3.181362827322018</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07850172633190991</v>
+        <v>0.07755592240020015</v>
       </c>
       <c r="W84">
-        <v>0.2172892929309357</v>
+        <v>0.2175123134980328</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4131669806942627</v>
+        <v>0.4081890652642113</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8471,22 +8471,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2178500932873342</v>
+        <v>0.2197500932873341</v>
       </c>
       <c r="C85">
-        <v>-886.872121560315</v>
+        <v>-906.9947138937952</v>
       </c>
       <c r="D85">
-        <v>276.7478784396852</v>
+        <v>273.7652861062051</v>
       </c>
       <c r="E85">
-        <v>1009.02</v>
+        <v>1026.16</v>
       </c>
       <c r="F85">
-        <v>1422.62</v>
+        <v>1439.76</v>
       </c>
       <c r="G85">
         <v>259</v>
@@ -8507,37 +8507,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M85">
-        <v>335.4537960000001</v>
+        <v>339.4954080000001</v>
       </c>
       <c r="N85">
-        <v>-198.5252245714286</v>
+        <v>-202.5668365714286</v>
       </c>
       <c r="O85">
-        <v>-37.71979266857144</v>
+        <v>-38.48769894857143</v>
       </c>
       <c r="P85">
-        <v>-160.8054319028572</v>
+        <v>-164.0791376228572</v>
       </c>
       <c r="Q85">
-        <v>-121.3054319028572</v>
+        <v>-124.5791376228572</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2194992534350995</v>
+        <v>0.2303554567747933</v>
       </c>
       <c r="T85">
-        <v>3.181362827322018</v>
+        <v>3.380198004029644</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07755592240020015</v>
+        <v>0.07663263760972157</v>
       </c>
       <c r="W85">
-        <v>0.2175123134980328</v>
+        <v>0.2177300240516276</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4081890652642113</v>
+        <v>0.4033296716301136</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8553,22 +8553,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2197500932873341</v>
+        <v>0.2216500932873341</v>
       </c>
       <c r="C86">
-        <v>-906.9947138937949</v>
+        <v>-927.053703166778</v>
       </c>
       <c r="D86">
-        <v>273.7652861062051</v>
+        <v>270.846296833222</v>
       </c>
       <c r="E86">
-        <v>1026.16</v>
+        <v>1043.3</v>
       </c>
       <c r="F86">
-        <v>1439.76</v>
+        <v>1456.9</v>
       </c>
       <c r="G86">
         <v>259</v>
@@ -8589,37 +8589,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M86">
-        <v>339.495408</v>
+        <v>343.53702</v>
       </c>
       <c r="N86">
-        <v>-202.5668365714286</v>
+        <v>-206.6084485714285</v>
       </c>
       <c r="O86">
-        <v>-38.48769894857143</v>
+        <v>-39.25560522857143</v>
       </c>
       <c r="P86">
-        <v>-164.0791376228571</v>
+        <v>-167.3528433428571</v>
       </c>
       <c r="Q86">
-        <v>-124.5791376228571</v>
+        <v>-127.8528433428571</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2303554567747931</v>
+        <v>0.2426591538931127</v>
       </c>
       <c r="T86">
-        <v>3.380198004029642</v>
+        <v>3.605544537631618</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0766326376097216</v>
+        <v>0.07573107716725427</v>
       </c>
       <c r="W86">
-        <v>0.2177300240516276</v>
+        <v>0.2179426120039615</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4033296716301136</v>
+        <v>0.3985846166697593</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8635,22 +8635,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2216500932873341</v>
+        <v>0.2235500932873342</v>
       </c>
       <c r="C87">
-        <v>-927.053703166778</v>
+        <v>-947.0511023955555</v>
       </c>
       <c r="D87">
-        <v>270.846296833222</v>
+        <v>267.9888976044444</v>
       </c>
       <c r="E87">
-        <v>1043.3</v>
+        <v>1060.44</v>
       </c>
       <c r="F87">
-        <v>1456.9</v>
+        <v>1474.04</v>
       </c>
       <c r="G87">
         <v>259</v>
@@ -8671,37 +8671,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M87">
-        <v>343.53702</v>
+        <v>347.578632</v>
       </c>
       <c r="N87">
-        <v>-206.6084485714285</v>
+        <v>-210.6500605714286</v>
       </c>
       <c r="O87">
-        <v>-39.25560522857143</v>
+        <v>-40.02351150857143</v>
       </c>
       <c r="P87">
-        <v>-167.3528433428571</v>
+        <v>-170.6265490628572</v>
       </c>
       <c r="Q87">
-        <v>-127.8528433428571</v>
+        <v>-131.1265490628572</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2426591538931127</v>
+        <v>0.256720522028335</v>
       </c>
       <c r="T87">
-        <v>3.605544537631618</v>
+        <v>3.863083433176734</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07573107716725427</v>
+        <v>0.07485048324670479</v>
       </c>
       <c r="W87">
-        <v>0.2179426120039615</v>
+        <v>0.218150256050427</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3985846166697593</v>
+        <v>0.3939499118247621</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8717,22 +8717,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2235500932873342</v>
+        <v>0.2254500932873341</v>
       </c>
       <c r="C88">
-        <v>-947.0511023955555</v>
+        <v>-966.9888405348404</v>
       </c>
       <c r="D88">
-        <v>267.9888976044444</v>
+        <v>265.1911594651597</v>
       </c>
       <c r="E88">
-        <v>1060.44</v>
+        <v>1077.58</v>
       </c>
       <c r="F88">
-        <v>1474.04</v>
+        <v>1491.18</v>
       </c>
       <c r="G88">
         <v>259</v>
@@ -8753,37 +8753,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M88">
-        <v>347.578632</v>
+        <v>351.620244</v>
       </c>
       <c r="N88">
-        <v>-210.6500605714286</v>
+        <v>-214.6916725714286</v>
       </c>
       <c r="O88">
-        <v>-40.02351150857143</v>
+        <v>-40.79141778857143</v>
       </c>
       <c r="P88">
-        <v>-170.6265490628572</v>
+        <v>-173.9002547828571</v>
       </c>
       <c r="Q88">
-        <v>-131.1265490628572</v>
+        <v>-134.4002547828571</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.256720522028335</v>
+        <v>0.2729451775689761</v>
       </c>
       <c r="T88">
-        <v>3.863083433176734</v>
+        <v>4.160243697267251</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07485048324670479</v>
+        <v>0.07399013286455877</v>
       </c>
       <c r="W88">
-        <v>0.218150256050427</v>
+        <v>0.2183531266705371</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3939499118247621</v>
+        <v>0.3894217519187304</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8799,22 +8799,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2254500932873341</v>
+        <v>0.2273500932873341</v>
       </c>
       <c r="C89">
-        <v>-966.9888405348404</v>
+        <v>-986.8687668203421</v>
       </c>
       <c r="D89">
-        <v>265.1911594651597</v>
+        <v>262.4512331796578</v>
       </c>
       <c r="E89">
-        <v>1077.58</v>
+        <v>1094.72</v>
       </c>
       <c r="F89">
-        <v>1491.18</v>
+        <v>1508.32</v>
       </c>
       <c r="G89">
         <v>259</v>
@@ -8835,37 +8835,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M89">
-        <v>351.620244</v>
+        <v>355.661856</v>
       </c>
       <c r="N89">
-        <v>-214.6916725714286</v>
+        <v>-218.7332845714286</v>
       </c>
       <c r="O89">
-        <v>-40.79141778857143</v>
+        <v>-41.55932406857143</v>
       </c>
       <c r="P89">
-        <v>-173.9002547828571</v>
+        <v>-177.1739605028571</v>
       </c>
       <c r="Q89">
-        <v>-134.4002547828571</v>
+        <v>-137.6739605028571</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2729451775689761</v>
+        <v>0.2918739423663909</v>
       </c>
       <c r="T89">
-        <v>4.160243697267251</v>
+        <v>4.506930672039523</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07399013286455877</v>
+        <v>0.07314933590018878</v>
       </c>
       <c r="W89">
-        <v>0.2183531266705371</v>
+        <v>0.2185513865947355</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3894217519187304</v>
+        <v>0.3849965047378358</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8881,22 +8881,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2273500932873341</v>
+        <v>0.2292500932873341</v>
       </c>
       <c r="C90">
-        <v>-986.8687668203421</v>
+        <v>-1006.692654844894</v>
       </c>
       <c r="D90">
-        <v>262.4512331796578</v>
+        <v>259.7673451551063</v>
       </c>
       <c r="E90">
-        <v>1094.72</v>
+        <v>1111.86</v>
       </c>
       <c r="F90">
-        <v>1508.32</v>
+        <v>1525.46</v>
       </c>
       <c r="G90">
         <v>259</v>
@@ -8917,37 +8917,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M90">
-        <v>355.661856</v>
+        <v>359.703468</v>
       </c>
       <c r="N90">
-        <v>-218.7332845714286</v>
+        <v>-222.7748965714286</v>
       </c>
       <c r="O90">
-        <v>-41.55932406857143</v>
+        <v>-42.32723034857143</v>
       </c>
       <c r="P90">
-        <v>-177.1739605028571</v>
+        <v>-180.4476662228572</v>
       </c>
       <c r="Q90">
-        <v>-137.6739605028571</v>
+        <v>-140.9476662228572</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2918739423663909</v>
+        <v>0.3142443007633356</v>
       </c>
       <c r="T90">
-        <v>4.506930672039523</v>
+        <v>4.916651642224935</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07314933590018878</v>
+        <v>0.07232743324962486</v>
       </c>
       <c r="W90">
-        <v>0.2185513865947355</v>
+        <v>0.2187451912397385</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3849965047378358</v>
+        <v>0.3806707013138151</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8963,22 +8963,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2292500932873341</v>
+        <v>0.2311500932873341</v>
       </c>
       <c r="C91">
-        <v>-1006.692654844894</v>
+        <v>-1026.462206387009</v>
       </c>
       <c r="D91">
-        <v>259.7673451551063</v>
+        <v>257.1377936129913</v>
       </c>
       <c r="E91">
-        <v>1111.86</v>
+        <v>1129</v>
       </c>
       <c r="F91">
-        <v>1525.46</v>
+        <v>1542.6</v>
       </c>
       <c r="G91">
         <v>259</v>
@@ -8999,37 +8999,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M91">
-        <v>359.703468</v>
+        <v>363.74508</v>
       </c>
       <c r="N91">
-        <v>-222.7748965714286</v>
+        <v>-226.8165085714286</v>
       </c>
       <c r="O91">
-        <v>-42.32723034857143</v>
+        <v>-43.09513662857143</v>
       </c>
       <c r="P91">
-        <v>-180.4476662228572</v>
+        <v>-183.7213719428572</v>
       </c>
       <c r="Q91">
-        <v>-140.9476662228572</v>
+        <v>-144.2213719428572</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3142443007633356</v>
+        <v>0.3410887308396691</v>
       </c>
       <c r="T91">
-        <v>4.916651642224935</v>
+        <v>5.408316806447429</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07232743324962486</v>
+        <v>0.07152379510240681</v>
       </c>
       <c r="W91">
-        <v>0.2187451912397385</v>
+        <v>0.2189346891148525</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3806707013138151</v>
+        <v>0.3764410268547727</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9045,22 +9045,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2311500932873341</v>
+        <v>0.2330500932873341</v>
       </c>
       <c r="C92">
-        <v>-1026.462206387009</v>
+        <v>-1046.179055009236</v>
       </c>
       <c r="D92">
-        <v>257.1377936129913</v>
+        <v>254.5609449907637</v>
       </c>
       <c r="E92">
-        <v>1129</v>
+        <v>1146.14</v>
       </c>
       <c r="F92">
-        <v>1542.6</v>
+        <v>1559.74</v>
       </c>
       <c r="G92">
         <v>259</v>
@@ -9081,37 +9081,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M92">
-        <v>363.74508</v>
+        <v>367.786692</v>
       </c>
       <c r="N92">
-        <v>-226.8165085714286</v>
+        <v>-230.8581205714286</v>
       </c>
       <c r="O92">
-        <v>-43.09513662857143</v>
+        <v>-43.86304290857143</v>
       </c>
       <c r="P92">
-        <v>-183.7213719428572</v>
+        <v>-186.9950776628571</v>
       </c>
       <c r="Q92">
-        <v>-144.2213719428572</v>
+        <v>-147.4950776628571</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3410887308396691</v>
+        <v>0.3738985898218546</v>
       </c>
       <c r="T92">
-        <v>5.408316806447429</v>
+        <v>6.009240896052699</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07152379510240681</v>
+        <v>0.07073781933205069</v>
       </c>
       <c r="W92">
-        <v>0.2189346891148525</v>
+        <v>0.2191200222015025</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3764410268547727</v>
+        <v>0.372304312273951</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9127,22 +9127,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2330500932873341</v>
+        <v>0.2349500932873341</v>
       </c>
       <c r="C93">
-        <v>-1046.179055009236</v>
+        <v>-1065.844769442304</v>
       </c>
       <c r="D93">
-        <v>254.5609449907637</v>
+        <v>252.0352305576962</v>
       </c>
       <c r="E93">
-        <v>1146.14</v>
+        <v>1163.28</v>
       </c>
       <c r="F93">
-        <v>1559.74</v>
+        <v>1576.88</v>
       </c>
       <c r="G93">
         <v>259</v>
@@ -9163,37 +9163,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M93">
-        <v>367.786692</v>
+        <v>371.8283040000001</v>
       </c>
       <c r="N93">
-        <v>-230.8581205714286</v>
+        <v>-234.8997325714286</v>
       </c>
       <c r="O93">
-        <v>-43.86304290857143</v>
+        <v>-44.63094918857144</v>
       </c>
       <c r="P93">
-        <v>-186.9950776628571</v>
+        <v>-190.2687833828572</v>
       </c>
       <c r="Q93">
-        <v>-147.4950776628571</v>
+        <v>-150.7687833828572</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3738985898218546</v>
+        <v>0.4149109135495865</v>
       </c>
       <c r="T93">
-        <v>6.009240896052699</v>
+        <v>6.760396008059288</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07073781933205069</v>
+        <v>0.06996892999148492</v>
       </c>
       <c r="W93">
-        <v>0.2191200222015025</v>
+        <v>0.2193013263080079</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.372304312273951</v>
+        <v>0.3682575262709732</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9209,22 +9209,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2349500932873341</v>
+        <v>0.2368500932873342</v>
       </c>
       <c r="C94">
-        <v>-1065.844769442304</v>
+        <v>-1085.460856769774</v>
       </c>
       <c r="D94">
-        <v>252.0352305576962</v>
+        <v>249.5591432302258</v>
       </c>
       <c r="E94">
-        <v>1163.28</v>
+        <v>1180.42</v>
       </c>
       <c r="F94">
-        <v>1576.88</v>
+        <v>1594.02</v>
       </c>
       <c r="G94">
         <v>259</v>
@@ -9245,37 +9245,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M94">
-        <v>371.8283040000001</v>
+        <v>375.869916</v>
       </c>
       <c r="N94">
-        <v>-234.8997325714286</v>
+        <v>-238.9413445714285</v>
       </c>
       <c r="O94">
-        <v>-44.63094918857144</v>
+        <v>-45.39885546857143</v>
       </c>
       <c r="P94">
-        <v>-190.2687833828572</v>
+        <v>-193.5424891028571</v>
       </c>
       <c r="Q94">
-        <v>-150.7687833828572</v>
+        <v>-154.0424891028571</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4149109135495865</v>
+        <v>0.4676410440566704</v>
       </c>
       <c r="T94">
-        <v>6.760396008059288</v>
+        <v>7.726166866353473</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06996892999148492</v>
+        <v>0.06921657590555498</v>
       </c>
       <c r="W94">
-        <v>0.2193013263080079</v>
+        <v>0.2194787314014701</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3682575262709732</v>
+        <v>0.3642977679239736</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9291,22 +9291,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2368500932873342</v>
+        <v>0.2387500932873342</v>
       </c>
       <c r="C95">
-        <v>-1085.460856769774</v>
+        <v>-1105.028765426809</v>
       </c>
       <c r="D95">
-        <v>249.5591432302258</v>
+        <v>247.131234573191</v>
       </c>
       <c r="E95">
-        <v>1180.42</v>
+        <v>1197.56</v>
       </c>
       <c r="F95">
-        <v>1594.02</v>
+        <v>1611.16</v>
       </c>
       <c r="G95">
         <v>259</v>
@@ -9327,37 +9327,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M95">
-        <v>375.869916</v>
+        <v>379.911528</v>
       </c>
       <c r="N95">
-        <v>-238.9413445714285</v>
+        <v>-242.9829565714286</v>
       </c>
       <c r="O95">
-        <v>-45.39885546857143</v>
+        <v>-46.16676174857143</v>
       </c>
       <c r="P95">
-        <v>-193.5424891028571</v>
+        <v>-196.8161948228571</v>
       </c>
       <c r="Q95">
-        <v>-154.0424891028571</v>
+        <v>-157.3161948228571</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4676410440566704</v>
+        <v>0.5379478847327822</v>
       </c>
       <c r="T95">
-        <v>7.726166866353473</v>
+        <v>9.013861344079055</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06921657590555498</v>
+        <v>0.06848022935336823</v>
       </c>
       <c r="W95">
-        <v>0.2194787314014701</v>
+        <v>0.2196523619184758</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3642977679239736</v>
+        <v>0.3604222597545695</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9373,22 +9373,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2387500932873342</v>
+        <v>0.2406500932873341</v>
       </c>
       <c r="C96">
-        <v>-1105.028765426809</v>
+        <v>-1124.54988802557</v>
       </c>
       <c r="D96">
-        <v>247.131234573191</v>
+        <v>244.7501119744299</v>
       </c>
       <c r="E96">
-        <v>1197.56</v>
+        <v>1214.7</v>
       </c>
       <c r="F96">
-        <v>1611.16</v>
+        <v>1628.3</v>
       </c>
       <c r="G96">
         <v>259</v>
@@ -9409,37 +9409,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M96">
-        <v>379.911528</v>
+        <v>383.9531400000001</v>
       </c>
       <c r="N96">
-        <v>-242.9829565714286</v>
+        <v>-247.0245685714286</v>
       </c>
       <c r="O96">
-        <v>-46.16676174857143</v>
+        <v>-46.93466802857144</v>
       </c>
       <c r="P96">
-        <v>-196.8161948228571</v>
+        <v>-200.0899005428572</v>
       </c>
       <c r="Q96">
-        <v>-157.3161948228571</v>
+        <v>-160.5899005428572</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5379478847327822</v>
+        <v>0.6363774616793388</v>
       </c>
       <c r="T96">
-        <v>9.013861344079055</v>
+        <v>10.81663361289487</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06848022935336823</v>
+        <v>0.06775938483385908</v>
       </c>
       <c r="W96">
-        <v>0.2196523619184758</v>
+        <v>0.219822337056176</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3604222597545695</v>
+        <v>0.3566283412308372</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9455,22 +9455,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2406500932873341</v>
+        <v>0.2425500932873342</v>
       </c>
       <c r="C97">
-        <v>-1124.54988802557</v>
+        <v>-1144.025564018844</v>
       </c>
       <c r="D97">
-        <v>244.7501119744299</v>
+        <v>242.4144359811563</v>
       </c>
       <c r="E97">
-        <v>1214.7</v>
+        <v>1231.84</v>
       </c>
       <c r="F97">
-        <v>1628.3</v>
+        <v>1645.44</v>
       </c>
       <c r="G97">
         <v>259</v>
@@ -9491,37 +9491,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M97">
-        <v>383.9531400000001</v>
+        <v>387.994752</v>
       </c>
       <c r="N97">
-        <v>-247.0245685714286</v>
+        <v>-251.0661805714286</v>
       </c>
       <c r="O97">
-        <v>-46.93466802857144</v>
+        <v>-47.70257430857143</v>
       </c>
       <c r="P97">
-        <v>-200.0899005428572</v>
+        <v>-203.3636062628571</v>
       </c>
       <c r="Q97">
-        <v>-160.5899005428572</v>
+        <v>-163.8636062628571</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6363774616793388</v>
+        <v>0.7840218270991739</v>
       </c>
       <c r="T97">
-        <v>10.81663361289487</v>
+        <v>13.52079201611859</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06775938483385908</v>
+        <v>0.06705355790850638</v>
       </c>
       <c r="W97">
-        <v>0.219822337056176</v>
+        <v>0.2199887710451742</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3566283412308372</v>
+        <v>0.3529134626763494</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9537,22 +9537,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2425500932873341</v>
+        <v>0.2444500932873342</v>
       </c>
       <c r="C98">
-        <v>-1144.025564018843</v>
+        <v>-1163.45708221259</v>
       </c>
       <c r="D98">
-        <v>242.4144359811563</v>
+        <v>240.12291778741</v>
       </c>
       <c r="E98">
-        <v>1231.84</v>
+        <v>1248.98</v>
       </c>
       <c r="F98">
-        <v>1645.44</v>
+        <v>1662.58</v>
       </c>
       <c r="G98">
         <v>259</v>
@@ -9573,37 +9573,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M98">
-        <v>387.9947519999999</v>
+        <v>392.036364</v>
       </c>
       <c r="N98">
-        <v>-251.0661805714285</v>
+        <v>-255.1077925714285</v>
       </c>
       <c r="O98">
-        <v>-47.70257430857141</v>
+        <v>-48.47048058857143</v>
       </c>
       <c r="P98">
-        <v>-203.3636062628571</v>
+        <v>-206.6373119828571</v>
       </c>
       <c r="Q98">
-        <v>-163.8636062628571</v>
+        <v>-167.1373119828571</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7840218270991719</v>
+        <v>1.030095769465563</v>
       </c>
       <c r="T98">
-        <v>13.52079201611856</v>
+        <v>18.02772268815808</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06705355790850639</v>
+        <v>0.06636228411563519</v>
       </c>
       <c r="W98">
-        <v>0.2199887710451742</v>
+        <v>0.2201517734055332</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3529134626763495</v>
+        <v>0.3492751795559746</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9619,22 +9619,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2444500932873342</v>
+        <v>0.2463500932873341</v>
       </c>
       <c r="C99">
-        <v>-1163.45708221259</v>
+        <v>-1182.845683137323</v>
       </c>
       <c r="D99">
-        <v>240.12291778741</v>
+        <v>237.8743168626771</v>
       </c>
       <c r="E99">
-        <v>1248.98</v>
+        <v>1266.12</v>
       </c>
       <c r="F99">
-        <v>1662.58</v>
+        <v>1679.72</v>
       </c>
       <c r="G99">
         <v>259</v>
@@ -9655,37 +9655,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M99">
-        <v>392.036364</v>
+        <v>396.077976</v>
       </c>
       <c r="N99">
-        <v>-255.1077925714285</v>
+        <v>-259.1494045714286</v>
       </c>
       <c r="O99">
-        <v>-48.47048058857143</v>
+        <v>-49.23838686857143</v>
       </c>
       <c r="P99">
-        <v>-206.6373119828571</v>
+        <v>-209.9110177028572</v>
       </c>
       <c r="Q99">
-        <v>-167.1373119828571</v>
+        <v>-170.4110177028572</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.030095769465563</v>
+        <v>1.522243654198344</v>
       </c>
       <c r="T99">
-        <v>18.02772268815808</v>
+        <v>27.04158403223711</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06636228411563519</v>
+        <v>0.06568511795118992</v>
       </c>
       <c r="W99">
-        <v>0.2201517734055332</v>
+        <v>0.2203114491871094</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3492751795559746</v>
+        <v>0.345711147111526</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9701,22 +9701,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2463500932873341</v>
+        <v>0.2482500932873341</v>
       </c>
       <c r="C100">
-        <v>-1182.845683137323</v>
+        <v>-1202.192561287485</v>
       </c>
       <c r="D100">
-        <v>237.8743168626771</v>
+        <v>235.6674387125144</v>
       </c>
       <c r="E100">
-        <v>1266.12</v>
+        <v>1283.26</v>
       </c>
       <c r="F100">
-        <v>1679.72</v>
+        <v>1696.86</v>
       </c>
       <c r="G100">
         <v>259</v>
@@ -9737,37 +9737,37 @@
         <v>136.9285714285714</v>
       </c>
       <c r="M100">
-        <v>396.077976</v>
+        <v>400.119588</v>
       </c>
       <c r="N100">
-        <v>-259.1494045714286</v>
+        <v>-263.1910165714285</v>
       </c>
       <c r="O100">
-        <v>-49.23838686857143</v>
+        <v>-50.00629314857142</v>
       </c>
       <c r="P100">
-        <v>-209.9110177028572</v>
+        <v>-213.1847234228571</v>
       </c>
       <c r="Q100">
-        <v>-170.4110177028572</v>
+        <v>-173.6847234228571</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.522243654198344</v>
+        <v>2.998687308396688</v>
       </c>
       <c r="T100">
-        <v>27.04158403223711</v>
+        <v>54.08316806447423</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06568511795118992</v>
+        <v>0.06502163191127894</v>
       </c>
       <c r="W100">
-        <v>0.2203114491871094</v>
+        <v>0.2204678991953204</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9775,91 +9775,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.345711147111526</v>
+        <v>0.3422191153225207</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2482500932873341</v>
-      </c>
-      <c r="C101">
-        <v>-1202.192561287485</v>
-      </c>
-      <c r="D101">
-        <v>235.6674387125144</v>
-      </c>
-      <c r="E101">
-        <v>1283.26</v>
-      </c>
-      <c r="F101">
-        <v>1696.86</v>
-      </c>
-      <c r="G101">
-        <v>259</v>
-      </c>
-      <c r="H101">
-        <v>1300.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>176.4285714285714</v>
-      </c>
-      <c r="K101">
-        <v>39.5</v>
-      </c>
-      <c r="L101">
-        <v>136.9285714285714</v>
-      </c>
-      <c r="M101">
-        <v>400.119588</v>
-      </c>
-      <c r="N101">
-        <v>-263.1910165714285</v>
-      </c>
-      <c r="O101">
-        <v>-50.00629314857142</v>
-      </c>
-      <c r="P101">
-        <v>-213.1847234228571</v>
-      </c>
-      <c r="Q101">
-        <v>-173.6847234228571</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.998687308396688</v>
-      </c>
-      <c r="T101">
-        <v>54.08316806447423</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06502163191127894</v>
-      </c>
-      <c r="W101">
-        <v>0.2204678991953204</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3422191153225207</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
